--- a/schedule_data/The Throw Down_ 5th Edition Team Schedules_may_27.xlsx
+++ b/schedule_data/The Throw Down_ 5th Edition Team Schedules_may_27.xlsx
@@ -24,8 +24,11 @@
     <sheet name="The Cleveland Show" sheetId="15" state="visible" r:id="rId15"/>
     <sheet name="The Incredibles" sheetId="16" state="visible" r:id="rId16"/>
     <sheet name="The Parkers" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet name="Court Assignment Printouts" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="17">'Court Assignment Printouts'!$A$1:$AE$174</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -33,7 +36,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="6">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,6 +62,51 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Times New Roman"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <sz val="25"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <u val="single"/>
+    </font>
+    <font>
+      <name val="Georgia"/>
     </font>
   </fonts>
   <fills count="6">
@@ -93,7 +141,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -101,11 +149,339 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="00000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thick">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thick">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thick">
+        <color rgb="00000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thick">
+        <color rgb="00000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -126,6 +502,70 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="18" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1606,10 +2046,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2172,10 +2612,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2738,10 +3178,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3304,10 +3744,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3870,10 +4310,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4436,10 +4876,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5002,10 +5442,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5568,12 +6008,7424 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:AD173"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="8.880000000000001" customWidth="1" min="7" max="7"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
+    <col width="8.880000000000001" customWidth="1" min="15" max="15"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+    <col width="13" customWidth="1" min="21" max="21"/>
+    <col width="13" customWidth="1" min="22" max="22"/>
+    <col width="8.880000000000001" customWidth="1" min="23" max="23"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="13" customWidth="1" min="26" max="26"/>
+    <col width="13" customWidth="1" min="27" max="27"/>
+    <col width="13" customWidth="1" min="28" max="28"/>
+    <col width="13" customWidth="1" min="29" max="29"/>
+    <col width="13" customWidth="1" min="30" max="30"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="22" t="n"/>
+      <c r="I1" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J1" s="21" t="n"/>
+      <c r="K1" s="21" t="n"/>
+      <c r="L1" s="21" t="n"/>
+      <c r="M1" s="21" t="n"/>
+      <c r="N1" s="22" t="n"/>
+      <c r="Q1" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R1" s="21" t="n"/>
+      <c r="S1" s="21" t="n"/>
+      <c r="T1" s="21" t="n"/>
+      <c r="U1" s="21" t="n"/>
+      <c r="V1" s="22" t="n"/>
+      <c r="Y1" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z1" s="21" t="n"/>
+      <c r="AA1" s="21" t="n"/>
+      <c r="AB1" s="21" t="n"/>
+      <c r="AC1" s="21" t="n"/>
+      <c r="AD1" s="22" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="n"/>
+      <c r="B2" s="24" t="n"/>
+      <c r="C2" s="24" t="n"/>
+      <c r="D2" s="24" t="n"/>
+      <c r="E2" s="24" t="n"/>
+      <c r="F2" s="25" t="n"/>
+      <c r="I2" s="23" t="n"/>
+      <c r="J2" s="24" t="n"/>
+      <c r="K2" s="24" t="n"/>
+      <c r="L2" s="24" t="n"/>
+      <c r="M2" s="24" t="n"/>
+      <c r="N2" s="25" t="n"/>
+      <c r="Q2" s="23" t="n"/>
+      <c r="R2" s="24" t="n"/>
+      <c r="S2" s="24" t="n"/>
+      <c r="T2" s="24" t="n"/>
+      <c r="U2" s="24" t="n"/>
+      <c r="V2" s="25" t="n"/>
+      <c r="Y2" s="23" t="n"/>
+      <c r="Z2" s="24" t="n"/>
+      <c r="AA2" s="24" t="n"/>
+      <c r="AB2" s="24" t="n"/>
+      <c r="AC2" s="24" t="n"/>
+      <c r="AD2" s="25" t="n"/>
+    </row>
+    <row r="3">
+      <c r="B3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" s="28" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K3" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="28" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="R3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S3" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="T3" s="28" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="Z3" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA3" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" s="28" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Sister Sister</t>
+        </is>
+      </c>
+      <c r="B4" s="11" t="n"/>
+      <c r="C4" s="11" t="n"/>
+      <c r="D4" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 2</t>
+        </is>
+      </c>
+      <c r="E4" s="11" t="n"/>
+      <c r="F4" s="11" t="n"/>
+      <c r="I4" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Abbott Elementary</t>
+        </is>
+      </c>
+      <c r="J4" s="11" t="n"/>
+      <c r="K4" s="11" t="n"/>
+      <c r="L4" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="M4" s="11" t="n"/>
+      <c r="N4" s="11" t="n"/>
+      <c r="Q4" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Martin</t>
+        </is>
+      </c>
+      <c r="R4" s="11" t="n"/>
+      <c r="S4" s="11" t="n"/>
+      <c r="T4" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="U4" s="11" t="n"/>
+      <c r="V4" s="11" t="n"/>
+      <c r="Y4" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="Z4" s="11" t="n"/>
+      <c r="AA4" s="11" t="n"/>
+      <c r="AB4" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="AC4" s="11" t="n"/>
+      <c r="AD4" s="11" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="31" t="inlineStr">
+        <is>
+          <t>Black Panther</t>
+        </is>
+      </c>
+      <c r="B5" s="11" t="n"/>
+      <c r="C5" s="11" t="n"/>
+      <c r="D5" s="31" t="inlineStr">
+        <is>
+          <t>Proud Family</t>
+        </is>
+      </c>
+      <c r="E5" s="11" t="n"/>
+      <c r="F5" s="11" t="n"/>
+      <c r="I5" s="31" t="inlineStr">
+        <is>
+          <t>Fresh Prince</t>
+        </is>
+      </c>
+      <c r="J5" s="11" t="n"/>
+      <c r="K5" s="11" t="n"/>
+      <c r="L5" s="31" t="inlineStr">
+        <is>
+          <t>Family Matters</t>
+        </is>
+      </c>
+      <c r="M5" s="11" t="n"/>
+      <c r="N5" s="11" t="n"/>
+      <c r="Q5" s="31" t="inlineStr">
+        <is>
+          <t>Fillmore</t>
+        </is>
+      </c>
+      <c r="R5" s="11" t="n"/>
+      <c r="S5" s="11" t="n"/>
+      <c r="T5" s="31" t="inlineStr">
+        <is>
+          <t>That's So Raven</t>
+        </is>
+      </c>
+      <c r="U5" s="11" t="n"/>
+      <c r="V5" s="11" t="n"/>
+      <c r="Y5" s="31" t="inlineStr">
+        <is>
+          <t>Smart Guy</t>
+        </is>
+      </c>
+      <c r="Z5" s="11" t="n"/>
+      <c r="AA5" s="11" t="n"/>
+      <c r="AB5" s="31" t="inlineStr">
+        <is>
+          <t>The Boondocks</t>
+        </is>
+      </c>
+      <c r="AC5" s="11" t="n"/>
+      <c r="AD5" s="11" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B6" s="11" t="n"/>
+      <c r="C6" s="11" t="n"/>
+      <c r="D6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E6" s="11" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="I6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J6" s="11" t="n"/>
+      <c r="K6" s="11" t="n"/>
+      <c r="L6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M6" s="11" t="n"/>
+      <c r="N6" s="11" t="n"/>
+      <c r="Q6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R6" s="11" t="n"/>
+      <c r="S6" s="11" t="n"/>
+      <c r="T6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U6" s="11" t="n"/>
+      <c r="V6" s="11" t="n"/>
+      <c r="Y6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z6" s="11" t="n"/>
+      <c r="AA6" s="11" t="n"/>
+      <c r="AB6" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC6" s="11" t="n"/>
+      <c r="AD6" s="11" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="n"/>
+      <c r="B7" s="11" t="n"/>
+      <c r="C7" s="11" t="n"/>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="11" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="11" t="n"/>
+      <c r="K7" s="11" t="n"/>
+      <c r="L7" s="11" t="n"/>
+      <c r="M7" s="11" t="n"/>
+      <c r="N7" s="11" t="n"/>
+      <c r="Q7" s="11" t="n"/>
+      <c r="R7" s="11" t="n"/>
+      <c r="S7" s="11" t="n"/>
+      <c r="T7" s="11" t="n"/>
+      <c r="U7" s="11" t="n"/>
+      <c r="V7" s="11" t="n"/>
+      <c r="Y7" s="11" t="n"/>
+      <c r="Z7" s="11" t="n"/>
+      <c r="AA7" s="11" t="n"/>
+      <c r="AB7" s="11" t="n"/>
+      <c r="AC7" s="11" t="n"/>
+      <c r="AD7" s="11" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="n"/>
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="11" t="n"/>
+      <c r="K8" s="11" t="n"/>
+      <c r="L8" s="11" t="n"/>
+      <c r="M8" s="11" t="n"/>
+      <c r="N8" s="11" t="n"/>
+      <c r="Q8" s="11" t="n"/>
+      <c r="R8" s="11" t="n"/>
+      <c r="S8" s="11" t="n"/>
+      <c r="T8" s="11" t="n"/>
+      <c r="U8" s="11" t="n"/>
+      <c r="V8" s="11" t="n"/>
+      <c r="Y8" s="11" t="n"/>
+      <c r="Z8" s="11" t="n"/>
+      <c r="AA8" s="11" t="n"/>
+      <c r="AB8" s="11" t="n"/>
+      <c r="AC8" s="11" t="n"/>
+      <c r="AD8" s="11" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="n"/>
+      <c r="B9" s="11" t="n"/>
+      <c r="C9" s="11" t="n"/>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="11" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="11" t="n"/>
+      <c r="K9" s="11" t="n"/>
+      <c r="L9" s="11" t="n"/>
+      <c r="M9" s="11" t="n"/>
+      <c r="N9" s="11" t="n"/>
+      <c r="Q9" s="11" t="n"/>
+      <c r="R9" s="11" t="n"/>
+      <c r="S9" s="11" t="n"/>
+      <c r="T9" s="11" t="n"/>
+      <c r="U9" s="11" t="n"/>
+      <c r="V9" s="11" t="n"/>
+      <c r="Y9" s="11" t="n"/>
+      <c r="Z9" s="11" t="n"/>
+      <c r="AA9" s="11" t="n"/>
+      <c r="AB9" s="11" t="n"/>
+      <c r="AC9" s="11" t="n"/>
+      <c r="AD9" s="11" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n"/>
+      <c r="C10" s="11" t="n"/>
+      <c r="D10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="E10" s="11" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 1</t>
+        </is>
+      </c>
+      <c r="J10" s="11" t="n"/>
+      <c r="K10" s="11" t="n"/>
+      <c r="L10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 3</t>
+        </is>
+      </c>
+      <c r="M10" s="11" t="n"/>
+      <c r="N10" s="11" t="n"/>
+      <c r="Q10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 2</t>
+        </is>
+      </c>
+      <c r="R10" s="11" t="n"/>
+      <c r="S10" s="11" t="n"/>
+      <c r="T10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="U10" s="11" t="n"/>
+      <c r="V10" s="11" t="n"/>
+      <c r="Y10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="Z10" s="11" t="n"/>
+      <c r="AA10" s="11" t="n"/>
+      <c r="AB10" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 4</t>
+        </is>
+      </c>
+      <c r="AC10" s="11" t="n"/>
+      <c r="AD10" s="11" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n"/>
+      <c r="C11" s="11" t="n"/>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="11" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="I11" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J11" s="11" t="n"/>
+      <c r="K11" s="11" t="n"/>
+      <c r="L11" s="11" t="n"/>
+      <c r="M11" s="11" t="n"/>
+      <c r="N11" s="11" t="n"/>
+      <c r="Q11" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R11" s="11" t="n"/>
+      <c r="S11" s="11" t="n"/>
+      <c r="T11" s="11" t="n"/>
+      <c r="U11" s="11" t="n"/>
+      <c r="V11" s="11" t="n"/>
+      <c r="Y11" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z11" s="11" t="n"/>
+      <c r="AA11" s="11" t="n"/>
+      <c r="AB11" s="11" t="n"/>
+      <c r="AC11" s="11" t="n"/>
+      <c r="AD11" s="11" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="I12" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="11" t="n"/>
+      <c r="L12" s="11" t="n"/>
+      <c r="M12" s="11" t="n"/>
+      <c r="N12" s="11" t="n"/>
+      <c r="Q12" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R12" s="11" t="n"/>
+      <c r="S12" s="11" t="n"/>
+      <c r="T12" s="11" t="n"/>
+      <c r="U12" s="11" t="n"/>
+      <c r="V12" s="11" t="n"/>
+      <c r="Y12" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z12" s="11" t="n"/>
+      <c r="AA12" s="11" t="n"/>
+      <c r="AB12" s="11" t="n"/>
+      <c r="AC12" s="11" t="n"/>
+      <c r="AD12" s="11" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="I13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="11" t="n"/>
+      <c r="L13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M13" s="11" t="n"/>
+      <c r="N13" s="11" t="n"/>
+      <c r="Q13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R13" s="11" t="n"/>
+      <c r="S13" s="11" t="n"/>
+      <c r="T13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U13" s="11" t="n"/>
+      <c r="V13" s="11" t="n"/>
+      <c r="Y13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z13" s="11" t="n"/>
+      <c r="AA13" s="11" t="n"/>
+      <c r="AB13" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC13" s="11" t="n"/>
+      <c r="AD13" s="11" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="11" t="n"/>
+      <c r="L14" s="11" t="n"/>
+      <c r="M14" s="11" t="n"/>
+      <c r="N14" s="11" t="n"/>
+      <c r="Q14" s="11" t="n"/>
+      <c r="R14" s="11" t="n"/>
+      <c r="S14" s="11" t="n"/>
+      <c r="T14" s="11" t="n"/>
+      <c r="U14" s="11" t="n"/>
+      <c r="V14" s="11" t="n"/>
+      <c r="Y14" s="11" t="n"/>
+      <c r="Z14" s="11" t="n"/>
+      <c r="AA14" s="11" t="n"/>
+      <c r="AB14" s="11" t="n"/>
+      <c r="AC14" s="11" t="n"/>
+      <c r="AD14" s="11" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B15" s="35" t="n"/>
+      <c r="C15" s="35" t="n"/>
+      <c r="D15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E15" s="35" t="n"/>
+      <c r="F15" s="35" t="n"/>
+      <c r="I15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J15" s="35" t="n"/>
+      <c r="K15" s="35" t="n"/>
+      <c r="L15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M15" s="35" t="n"/>
+      <c r="N15" s="35" t="n"/>
+      <c r="Q15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R15" s="35" t="n"/>
+      <c r="S15" s="35" t="n"/>
+      <c r="T15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U15" s="35" t="n"/>
+      <c r="V15" s="35" t="n"/>
+      <c r="Y15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z15" s="35" t="n"/>
+      <c r="AA15" s="35" t="n"/>
+      <c r="AB15" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC15" s="35" t="n"/>
+      <c r="AD15" s="35" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="35" t="n"/>
+      <c r="B16" s="35" t="n"/>
+      <c r="C16" s="35" t="n"/>
+      <c r="D16" s="35" t="n"/>
+      <c r="E16" s="35" t="n"/>
+      <c r="F16" s="35" t="n"/>
+      <c r="I16" s="35" t="n"/>
+      <c r="J16" s="35" t="n"/>
+      <c r="K16" s="35" t="n"/>
+      <c r="L16" s="35" t="n"/>
+      <c r="M16" s="35" t="n"/>
+      <c r="N16" s="35" t="n"/>
+      <c r="Q16" s="35" t="n"/>
+      <c r="R16" s="35" t="n"/>
+      <c r="S16" s="35" t="n"/>
+      <c r="T16" s="35" t="n"/>
+      <c r="U16" s="35" t="n"/>
+      <c r="V16" s="35" t="n"/>
+      <c r="Y16" s="35" t="n"/>
+      <c r="Z16" s="35" t="n"/>
+      <c r="AA16" s="35" t="n"/>
+      <c r="AB16" s="35" t="n"/>
+      <c r="AC16" s="35" t="n"/>
+      <c r="AD16" s="35" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="21" t="n"/>
+      <c r="E18" s="21" t="n"/>
+      <c r="F18" s="22" t="n"/>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="n"/>
+      <c r="K18" s="21" t="n"/>
+      <c r="L18" s="21" t="n"/>
+      <c r="M18" s="21" t="n"/>
+      <c r="N18" s="22" t="n"/>
+      <c r="Q18" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R18" s="21" t="n"/>
+      <c r="S18" s="21" t="n"/>
+      <c r="T18" s="21" t="n"/>
+      <c r="U18" s="21" t="n"/>
+      <c r="V18" s="22" t="n"/>
+      <c r="Y18" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z18" s="21" t="n"/>
+      <c r="AA18" s="21" t="n"/>
+      <c r="AB18" s="21" t="n"/>
+      <c r="AC18" s="21" t="n"/>
+      <c r="AD18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="24" t="n"/>
+      <c r="F19" s="25" t="n"/>
+      <c r="I19" s="23" t="n"/>
+      <c r="J19" s="24" t="n"/>
+      <c r="K19" s="24" t="n"/>
+      <c r="L19" s="24" t="n"/>
+      <c r="M19" s="24" t="n"/>
+      <c r="N19" s="25" t="n"/>
+      <c r="Q19" s="23" t="n"/>
+      <c r="R19" s="24" t="n"/>
+      <c r="S19" s="24" t="n"/>
+      <c r="T19" s="24" t="n"/>
+      <c r="U19" s="24" t="n"/>
+      <c r="V19" s="25" t="n"/>
+      <c r="Y19" s="23" t="n"/>
+      <c r="Z19" s="24" t="n"/>
+      <c r="AA19" s="24" t="n"/>
+      <c r="AB19" s="24" t="n"/>
+      <c r="AC19" s="24" t="n"/>
+      <c r="AD19" s="25" t="n"/>
+    </row>
+    <row r="20">
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" s="28" t="n">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="J20" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="L20" s="28" t="n">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="R20" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="T20" s="28" t="n">
+        <v>0.3923611111111111</v>
+      </c>
+      <c r="Z20" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA20" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="AB20" s="28" t="n">
+        <v>0.3923611111111111</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Fresh Prince</t>
+        </is>
+      </c>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 1</t>
+        </is>
+      </c>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="I21" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Fillmore</t>
+        </is>
+      </c>
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="11" t="n"/>
+      <c r="L21" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="M21" s="11" t="n"/>
+      <c r="N21" s="11" t="n"/>
+      <c r="Q21" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Family Matters</t>
+        </is>
+      </c>
+      <c r="R21" s="11" t="n"/>
+      <c r="S21" s="11" t="n"/>
+      <c r="T21" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 2</t>
+        </is>
+      </c>
+      <c r="U21" s="11" t="n"/>
+      <c r="V21" s="11" t="n"/>
+      <c r="Y21" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Boondocks</t>
+        </is>
+      </c>
+      <c r="Z21" s="11" t="n"/>
+      <c r="AA21" s="11" t="n"/>
+      <c r="AB21" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="AC21" s="11" t="n"/>
+      <c r="AD21" s="11" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="31" t="inlineStr">
+        <is>
+          <t>The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="31" t="inlineStr">
+        <is>
+          <t>The Parkers</t>
+        </is>
+      </c>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="I22" s="31" t="inlineStr">
+        <is>
+          <t>Sister Sister</t>
+        </is>
+      </c>
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="11" t="n"/>
+      <c r="L22" s="31" t="inlineStr">
+        <is>
+          <t>Static Shock</t>
+        </is>
+      </c>
+      <c r="M22" s="11" t="n"/>
+      <c r="N22" s="11" t="n"/>
+      <c r="Q22" s="31" t="inlineStr">
+        <is>
+          <t>Abbott Elementary</t>
+        </is>
+      </c>
+      <c r="R22" s="11" t="n"/>
+      <c r="S22" s="11" t="n"/>
+      <c r="T22" s="31" t="inlineStr">
+        <is>
+          <t>The Incredibles</t>
+        </is>
+      </c>
+      <c r="U22" s="11" t="n"/>
+      <c r="V22" s="11" t="n"/>
+      <c r="Y22" s="31" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="Z22" s="11" t="n"/>
+      <c r="AA22" s="11" t="n"/>
+      <c r="AB22" s="31" t="inlineStr">
+        <is>
+          <t>Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="AC22" s="11" t="n"/>
+      <c r="AD22" s="11" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="I23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="11" t="n"/>
+      <c r="L23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M23" s="11" t="n"/>
+      <c r="N23" s="11" t="n"/>
+      <c r="Q23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R23" s="11" t="n"/>
+      <c r="S23" s="11" t="n"/>
+      <c r="T23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U23" s="11" t="n"/>
+      <c r="V23" s="11" t="n"/>
+      <c r="Y23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z23" s="11" t="n"/>
+      <c r="AA23" s="11" t="n"/>
+      <c r="AB23" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC23" s="11" t="n"/>
+      <c r="AD23" s="11" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="11" t="n"/>
+      <c r="L24" s="11" t="n"/>
+      <c r="M24" s="11" t="n"/>
+      <c r="N24" s="11" t="n"/>
+      <c r="Q24" s="11" t="n"/>
+      <c r="R24" s="11" t="n"/>
+      <c r="S24" s="11" t="n"/>
+      <c r="T24" s="11" t="n"/>
+      <c r="U24" s="11" t="n"/>
+      <c r="V24" s="11" t="n"/>
+      <c r="Y24" s="11" t="n"/>
+      <c r="Z24" s="11" t="n"/>
+      <c r="AA24" s="11" t="n"/>
+      <c r="AB24" s="11" t="n"/>
+      <c r="AC24" s="11" t="n"/>
+      <c r="AD24" s="11" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="11" t="n"/>
+      <c r="L25" s="11" t="n"/>
+      <c r="M25" s="11" t="n"/>
+      <c r="N25" s="11" t="n"/>
+      <c r="Q25" s="11" t="n"/>
+      <c r="R25" s="11" t="n"/>
+      <c r="S25" s="11" t="n"/>
+      <c r="T25" s="11" t="n"/>
+      <c r="U25" s="11" t="n"/>
+      <c r="V25" s="11" t="n"/>
+      <c r="Y25" s="11" t="n"/>
+      <c r="Z25" s="11" t="n"/>
+      <c r="AA25" s="11" t="n"/>
+      <c r="AB25" s="11" t="n"/>
+      <c r="AC25" s="11" t="n"/>
+      <c r="AD25" s="11" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="I26" s="11" t="n"/>
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="11" t="n"/>
+      <c r="L26" s="11" t="n"/>
+      <c r="M26" s="11" t="n"/>
+      <c r="N26" s="11" t="n"/>
+      <c r="Q26" s="11" t="n"/>
+      <c r="R26" s="11" t="n"/>
+      <c r="S26" s="11" t="n"/>
+      <c r="T26" s="11" t="n"/>
+      <c r="U26" s="11" t="n"/>
+      <c r="V26" s="11" t="n"/>
+      <c r="Y26" s="11" t="n"/>
+      <c r="Z26" s="11" t="n"/>
+      <c r="AA26" s="11" t="n"/>
+      <c r="AB26" s="11" t="n"/>
+      <c r="AC26" s="11" t="n"/>
+      <c r="AD26" s="11" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 1</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="I27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Court 1</t>
+        </is>
+      </c>
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="11" t="n"/>
+      <c r="L27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 2</t>
+        </is>
+      </c>
+      <c r="M27" s="11" t="n"/>
+      <c r="N27" s="11" t="n"/>
+      <c r="Q27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R27" s="11" t="n"/>
+      <c r="S27" s="11" t="n"/>
+      <c r="T27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 4</t>
+        </is>
+      </c>
+      <c r="U27" s="11" t="n"/>
+      <c r="V27" s="11" t="n"/>
+      <c r="Y27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="Z27" s="11" t="n"/>
+      <c r="AA27" s="11" t="n"/>
+      <c r="AB27" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 3</t>
+        </is>
+      </c>
+      <c r="AC27" s="11" t="n"/>
+      <c r="AD27" s="11" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="I28" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="11" t="n"/>
+      <c r="L28" s="11" t="n"/>
+      <c r="M28" s="11" t="n"/>
+      <c r="N28" s="11" t="n"/>
+      <c r="Q28" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R28" s="11" t="n"/>
+      <c r="S28" s="11" t="n"/>
+      <c r="T28" s="11" t="n"/>
+      <c r="U28" s="11" t="n"/>
+      <c r="V28" s="11" t="n"/>
+      <c r="Y28" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z28" s="11" t="n"/>
+      <c r="AA28" s="11" t="n"/>
+      <c r="AB28" s="11" t="n"/>
+      <c r="AC28" s="11" t="n"/>
+      <c r="AD28" s="11" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="I29" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="11" t="n"/>
+      <c r="L29" s="11" t="n"/>
+      <c r="M29" s="11" t="n"/>
+      <c r="N29" s="11" t="n"/>
+      <c r="Q29" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R29" s="11" t="n"/>
+      <c r="S29" s="11" t="n"/>
+      <c r="T29" s="11" t="n"/>
+      <c r="U29" s="11" t="n"/>
+      <c r="V29" s="11" t="n"/>
+      <c r="Y29" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z29" s="11" t="n"/>
+      <c r="AA29" s="11" t="n"/>
+      <c r="AB29" s="11" t="n"/>
+      <c r="AC29" s="11" t="n"/>
+      <c r="AD29" s="11" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="I30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="11" t="n"/>
+      <c r="L30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M30" s="11" t="n"/>
+      <c r="N30" s="11" t="n"/>
+      <c r="Q30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R30" s="11" t="n"/>
+      <c r="S30" s="11" t="n"/>
+      <c r="T30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U30" s="11" t="n"/>
+      <c r="V30" s="11" t="n"/>
+      <c r="Y30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z30" s="11" t="n"/>
+      <c r="AA30" s="11" t="n"/>
+      <c r="AB30" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC30" s="11" t="n"/>
+      <c r="AD30" s="11" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="11" t="n"/>
+      <c r="L31" s="11" t="n"/>
+      <c r="M31" s="11" t="n"/>
+      <c r="N31" s="11" t="n"/>
+      <c r="Q31" s="11" t="n"/>
+      <c r="R31" s="11" t="n"/>
+      <c r="S31" s="11" t="n"/>
+      <c r="T31" s="11" t="n"/>
+      <c r="U31" s="11" t="n"/>
+      <c r="V31" s="11" t="n"/>
+      <c r="Y31" s="11" t="n"/>
+      <c r="Z31" s="11" t="n"/>
+      <c r="AA31" s="11" t="n"/>
+      <c r="AB31" s="11" t="n"/>
+      <c r="AC31" s="11" t="n"/>
+      <c r="AD31" s="11" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B32" s="35" t="n"/>
+      <c r="C32" s="35" t="n"/>
+      <c r="D32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E32" s="35" t="n"/>
+      <c r="F32" s="35" t="n"/>
+      <c r="I32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J32" s="35" t="n"/>
+      <c r="K32" s="35" t="n"/>
+      <c r="L32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M32" s="35" t="n"/>
+      <c r="N32" s="35" t="n"/>
+      <c r="Q32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R32" s="35" t="n"/>
+      <c r="S32" s="35" t="n"/>
+      <c r="T32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U32" s="35" t="n"/>
+      <c r="V32" s="35" t="n"/>
+      <c r="Y32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z32" s="35" t="n"/>
+      <c r="AA32" s="35" t="n"/>
+      <c r="AB32" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC32" s="35" t="n"/>
+      <c r="AD32" s="35" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="35" t="n"/>
+      <c r="B33" s="35" t="n"/>
+      <c r="C33" s="35" t="n"/>
+      <c r="D33" s="35" t="n"/>
+      <c r="E33" s="35" t="n"/>
+      <c r="F33" s="35" t="n"/>
+      <c r="I33" s="35" t="n"/>
+      <c r="J33" s="35" t="n"/>
+      <c r="K33" s="35" t="n"/>
+      <c r="L33" s="35" t="n"/>
+      <c r="M33" s="35" t="n"/>
+      <c r="N33" s="35" t="n"/>
+      <c r="Q33" s="35" t="n"/>
+      <c r="R33" s="35" t="n"/>
+      <c r="S33" s="35" t="n"/>
+      <c r="T33" s="35" t="n"/>
+      <c r="U33" s="35" t="n"/>
+      <c r="V33" s="35" t="n"/>
+      <c r="Y33" s="35" t="n"/>
+      <c r="Z33" s="35" t="n"/>
+      <c r="AA33" s="35" t="n"/>
+      <c r="AB33" s="35" t="n"/>
+      <c r="AC33" s="35" t="n"/>
+      <c r="AD33" s="35" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B36" s="21" t="n"/>
+      <c r="C36" s="21" t="n"/>
+      <c r="D36" s="21" t="n"/>
+      <c r="E36" s="21" t="n"/>
+      <c r="F36" s="22" t="n"/>
+      <c r="I36" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J36" s="21" t="n"/>
+      <c r="K36" s="21" t="n"/>
+      <c r="L36" s="21" t="n"/>
+      <c r="M36" s="21" t="n"/>
+      <c r="N36" s="22" t="n"/>
+      <c r="Q36" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R36" s="21" t="n"/>
+      <c r="S36" s="21" t="n"/>
+      <c r="T36" s="21" t="n"/>
+      <c r="U36" s="21" t="n"/>
+      <c r="V36" s="22" t="n"/>
+      <c r="Y36" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z36" s="21" t="n"/>
+      <c r="AA36" s="21" t="n"/>
+      <c r="AB36" s="21" t="n"/>
+      <c r="AC36" s="21" t="n"/>
+      <c r="AD36" s="22" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="23" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="24" t="n"/>
+      <c r="F37" s="25" t="n"/>
+      <c r="I37" s="23" t="n"/>
+      <c r="J37" s="24" t="n"/>
+      <c r="K37" s="24" t="n"/>
+      <c r="L37" s="24" t="n"/>
+      <c r="M37" s="24" t="n"/>
+      <c r="N37" s="25" t="n"/>
+      <c r="Q37" s="23" t="n"/>
+      <c r="R37" s="24" t="n"/>
+      <c r="S37" s="24" t="n"/>
+      <c r="T37" s="24" t="n"/>
+      <c r="U37" s="24" t="n"/>
+      <c r="V37" s="25" t="n"/>
+      <c r="Y37" s="23" t="n"/>
+      <c r="Z37" s="24" t="n"/>
+      <c r="AA37" s="24" t="n"/>
+      <c r="AB37" s="24" t="n"/>
+      <c r="AC37" s="24" t="n"/>
+      <c r="AD37" s="25" t="n"/>
+    </row>
+    <row r="38">
+      <c r="B38" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C38" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D38" s="28" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="J38" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K38" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="L38" s="28" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="R38" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S38" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T38" s="28" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+      <c r="Z38" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA38" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB38" s="28" t="n">
+        <v>0.4166666666666667</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Parkers</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="I39" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Smart Guy</t>
+        </is>
+      </c>
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="11" t="n"/>
+      <c r="L39" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="n"/>
+      <c r="N39" s="11" t="n"/>
+      <c r="Q39" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Proud Family</t>
+        </is>
+      </c>
+      <c r="R39" s="11" t="n"/>
+      <c r="S39" s="11" t="n"/>
+      <c r="T39" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 1</t>
+        </is>
+      </c>
+      <c r="U39" s="11" t="n"/>
+      <c r="V39" s="11" t="n"/>
+      <c r="Y39" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Incredibles</t>
+        </is>
+      </c>
+      <c r="Z39" s="11" t="n"/>
+      <c r="AA39" s="11" t="n"/>
+      <c r="AB39" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="AC39" s="11" t="n"/>
+      <c r="AD39" s="11" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="31" t="inlineStr">
+        <is>
+          <t>Fresh Prince</t>
+        </is>
+      </c>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="31" t="inlineStr">
+        <is>
+          <t>Sister Sister</t>
+        </is>
+      </c>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="I40" s="31" t="inlineStr">
+        <is>
+          <t>Family Matters</t>
+        </is>
+      </c>
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="11" t="n"/>
+      <c r="L40" s="31" t="inlineStr">
+        <is>
+          <t>Static Shock</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="n"/>
+      <c r="N40" s="11" t="n"/>
+      <c r="Q40" s="31" t="inlineStr">
+        <is>
+          <t>Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="R40" s="11" t="n"/>
+      <c r="S40" s="11" t="n"/>
+      <c r="T40" s="31" t="inlineStr">
+        <is>
+          <t>The Boondocks</t>
+        </is>
+      </c>
+      <c r="U40" s="11" t="n"/>
+      <c r="V40" s="11" t="n"/>
+      <c r="Y40" s="31" t="inlineStr">
+        <is>
+          <t>Black Panther</t>
+        </is>
+      </c>
+      <c r="Z40" s="11" t="n"/>
+      <c r="AA40" s="11" t="n"/>
+      <c r="AB40" s="31" t="inlineStr">
+        <is>
+          <t>Fillmore</t>
+        </is>
+      </c>
+      <c r="AC40" s="11" t="n"/>
+      <c r="AD40" s="11" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="I41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="11" t="n"/>
+      <c r="L41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="n"/>
+      <c r="N41" s="11" t="n"/>
+      <c r="Q41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R41" s="11" t="n"/>
+      <c r="S41" s="11" t="n"/>
+      <c r="T41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U41" s="11" t="n"/>
+      <c r="V41" s="11" t="n"/>
+      <c r="Y41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z41" s="11" t="n"/>
+      <c r="AA41" s="11" t="n"/>
+      <c r="AB41" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC41" s="11" t="n"/>
+      <c r="AD41" s="11" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="11" t="n"/>
+      <c r="L42" s="11" t="n"/>
+      <c r="M42" s="11" t="n"/>
+      <c r="N42" s="11" t="n"/>
+      <c r="Q42" s="11" t="n"/>
+      <c r="R42" s="11" t="n"/>
+      <c r="S42" s="11" t="n"/>
+      <c r="T42" s="11" t="n"/>
+      <c r="U42" s="11" t="n"/>
+      <c r="V42" s="11" t="n"/>
+      <c r="Y42" s="11" t="n"/>
+      <c r="Z42" s="11" t="n"/>
+      <c r="AA42" s="11" t="n"/>
+      <c r="AB42" s="11" t="n"/>
+      <c r="AC42" s="11" t="n"/>
+      <c r="AD42" s="11" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="11" t="n"/>
+      <c r="L43" s="11" t="n"/>
+      <c r="M43" s="11" t="n"/>
+      <c r="N43" s="11" t="n"/>
+      <c r="Q43" s="11" t="n"/>
+      <c r="R43" s="11" t="n"/>
+      <c r="S43" s="11" t="n"/>
+      <c r="T43" s="11" t="n"/>
+      <c r="U43" s="11" t="n"/>
+      <c r="V43" s="11" t="n"/>
+      <c r="Y43" s="11" t="n"/>
+      <c r="Z43" s="11" t="n"/>
+      <c r="AA43" s="11" t="n"/>
+      <c r="AB43" s="11" t="n"/>
+      <c r="AC43" s="11" t="n"/>
+      <c r="AD43" s="11" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="n"/>
+      <c r="B44" s="11" t="n"/>
+      <c r="C44" s="11" t="n"/>
+      <c r="D44" s="11" t="n"/>
+      <c r="E44" s="11" t="n"/>
+      <c r="F44" s="11" t="n"/>
+      <c r="I44" s="11" t="n"/>
+      <c r="J44" s="11" t="n"/>
+      <c r="K44" s="11" t="n"/>
+      <c r="L44" s="11" t="n"/>
+      <c r="M44" s="11" t="n"/>
+      <c r="N44" s="11" t="n"/>
+      <c r="Q44" s="11" t="n"/>
+      <c r="R44" s="11" t="n"/>
+      <c r="S44" s="11" t="n"/>
+      <c r="T44" s="11" t="n"/>
+      <c r="U44" s="11" t="n"/>
+      <c r="V44" s="11" t="n"/>
+      <c r="Y44" s="11" t="n"/>
+      <c r="Z44" s="11" t="n"/>
+      <c r="AA44" s="11" t="n"/>
+      <c r="AB44" s="11" t="n"/>
+      <c r="AC44" s="11" t="n"/>
+      <c r="AD44" s="11" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 4</t>
+        </is>
+      </c>
+      <c r="B45" s="11" t="n"/>
+      <c r="C45" s="11" t="n"/>
+      <c r="D45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="E45" s="11" t="n"/>
+      <c r="F45" s="11" t="n"/>
+      <c r="I45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="J45" s="11" t="n"/>
+      <c r="K45" s="11" t="n"/>
+      <c r="L45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 1</t>
+        </is>
+      </c>
+      <c r="M45" s="11" t="n"/>
+      <c r="N45" s="11" t="n"/>
+      <c r="Q45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R45" s="11" t="n"/>
+      <c r="S45" s="11" t="n"/>
+      <c r="T45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 3</t>
+        </is>
+      </c>
+      <c r="U45" s="11" t="n"/>
+      <c r="V45" s="11" t="n"/>
+      <c r="Y45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 2</t>
+        </is>
+      </c>
+      <c r="Z45" s="11" t="n"/>
+      <c r="AA45" s="11" t="n"/>
+      <c r="AB45" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="AC45" s="11" t="n"/>
+      <c r="AD45" s="11" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n"/>
+      <c r="C46" s="11" t="n"/>
+      <c r="D46" s="11" t="n"/>
+      <c r="E46" s="11" t="n"/>
+      <c r="F46" s="11" t="n"/>
+      <c r="I46" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J46" s="11" t="n"/>
+      <c r="K46" s="11" t="n"/>
+      <c r="L46" s="11" t="n"/>
+      <c r="M46" s="11" t="n"/>
+      <c r="N46" s="11" t="n"/>
+      <c r="Q46" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R46" s="11" t="n"/>
+      <c r="S46" s="11" t="n"/>
+      <c r="T46" s="11" t="n"/>
+      <c r="U46" s="11" t="n"/>
+      <c r="V46" s="11" t="n"/>
+      <c r="Y46" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z46" s="11" t="n"/>
+      <c r="AA46" s="11" t="n"/>
+      <c r="AB46" s="11" t="n"/>
+      <c r="AC46" s="11" t="n"/>
+      <c r="AD46" s="11" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B47" s="11" t="n"/>
+      <c r="C47" s="11" t="n"/>
+      <c r="D47" s="11" t="n"/>
+      <c r="E47" s="11" t="n"/>
+      <c r="F47" s="11" t="n"/>
+      <c r="I47" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J47" s="11" t="n"/>
+      <c r="K47" s="11" t="n"/>
+      <c r="L47" s="11" t="n"/>
+      <c r="M47" s="11" t="n"/>
+      <c r="N47" s="11" t="n"/>
+      <c r="Q47" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R47" s="11" t="n"/>
+      <c r="S47" s="11" t="n"/>
+      <c r="T47" s="11" t="n"/>
+      <c r="U47" s="11" t="n"/>
+      <c r="V47" s="11" t="n"/>
+      <c r="Y47" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z47" s="11" t="n"/>
+      <c r="AA47" s="11" t="n"/>
+      <c r="AB47" s="11" t="n"/>
+      <c r="AC47" s="11" t="n"/>
+      <c r="AD47" s="11" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="n"/>
+      <c r="C48" s="11" t="n"/>
+      <c r="D48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E48" s="11" t="n"/>
+      <c r="F48" s="11" t="n"/>
+      <c r="I48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J48" s="11" t="n"/>
+      <c r="K48" s="11" t="n"/>
+      <c r="L48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="n"/>
+      <c r="N48" s="11" t="n"/>
+      <c r="Q48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R48" s="11" t="n"/>
+      <c r="S48" s="11" t="n"/>
+      <c r="T48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U48" s="11" t="n"/>
+      <c r="V48" s="11" t="n"/>
+      <c r="Y48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z48" s="11" t="n"/>
+      <c r="AA48" s="11" t="n"/>
+      <c r="AB48" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC48" s="11" t="n"/>
+      <c r="AD48" s="11" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="11" t="n"/>
+      <c r="B49" s="11" t="n"/>
+      <c r="C49" s="11" t="n"/>
+      <c r="D49" s="11" t="n"/>
+      <c r="E49" s="11" t="n"/>
+      <c r="F49" s="11" t="n"/>
+      <c r="I49" s="11" t="n"/>
+      <c r="J49" s="11" t="n"/>
+      <c r="K49" s="11" t="n"/>
+      <c r="L49" s="11" t="n"/>
+      <c r="M49" s="11" t="n"/>
+      <c r="N49" s="11" t="n"/>
+      <c r="Q49" s="11" t="n"/>
+      <c r="R49" s="11" t="n"/>
+      <c r="S49" s="11" t="n"/>
+      <c r="T49" s="11" t="n"/>
+      <c r="U49" s="11" t="n"/>
+      <c r="V49" s="11" t="n"/>
+      <c r="Y49" s="11" t="n"/>
+      <c r="Z49" s="11" t="n"/>
+      <c r="AA49" s="11" t="n"/>
+      <c r="AB49" s="11" t="n"/>
+      <c r="AC49" s="11" t="n"/>
+      <c r="AD49" s="11" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B50" s="35" t="n"/>
+      <c r="C50" s="35" t="n"/>
+      <c r="D50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E50" s="35" t="n"/>
+      <c r="F50" s="35" t="n"/>
+      <c r="I50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J50" s="35" t="n"/>
+      <c r="K50" s="35" t="n"/>
+      <c r="L50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M50" s="35" t="n"/>
+      <c r="N50" s="35" t="n"/>
+      <c r="Q50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R50" s="35" t="n"/>
+      <c r="S50" s="35" t="n"/>
+      <c r="T50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U50" s="35" t="n"/>
+      <c r="V50" s="35" t="n"/>
+      <c r="Y50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z50" s="35" t="n"/>
+      <c r="AA50" s="35" t="n"/>
+      <c r="AB50" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC50" s="35" t="n"/>
+      <c r="AD50" s="35" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="35" t="n"/>
+      <c r="B51" s="35" t="n"/>
+      <c r="C51" s="35" t="n"/>
+      <c r="D51" s="35" t="n"/>
+      <c r="E51" s="35" t="n"/>
+      <c r="F51" s="35" t="n"/>
+      <c r="I51" s="35" t="n"/>
+      <c r="J51" s="35" t="n"/>
+      <c r="K51" s="35" t="n"/>
+      <c r="L51" s="35" t="n"/>
+      <c r="M51" s="35" t="n"/>
+      <c r="N51" s="35" t="n"/>
+      <c r="Q51" s="35" t="n"/>
+      <c r="R51" s="35" t="n"/>
+      <c r="S51" s="35" t="n"/>
+      <c r="T51" s="35" t="n"/>
+      <c r="U51" s="35" t="n"/>
+      <c r="V51" s="35" t="n"/>
+      <c r="Y51" s="35" t="n"/>
+      <c r="Z51" s="35" t="n"/>
+      <c r="AA51" s="35" t="n"/>
+      <c r="AB51" s="35" t="n"/>
+      <c r="AC51" s="35" t="n"/>
+      <c r="AD51" s="35" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="n"/>
+      <c r="C53" s="21" t="n"/>
+      <c r="D53" s="21" t="n"/>
+      <c r="E53" s="21" t="n"/>
+      <c r="F53" s="22" t="n"/>
+      <c r="I53" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J53" s="21" t="n"/>
+      <c r="K53" s="21" t="n"/>
+      <c r="L53" s="21" t="n"/>
+      <c r="M53" s="21" t="n"/>
+      <c r="N53" s="22" t="n"/>
+      <c r="Q53" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R53" s="21" t="n"/>
+      <c r="S53" s="21" t="n"/>
+      <c r="T53" s="21" t="n"/>
+      <c r="U53" s="21" t="n"/>
+      <c r="V53" s="22" t="n"/>
+      <c r="Y53" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z53" s="21" t="n"/>
+      <c r="AA53" s="21" t="n"/>
+      <c r="AB53" s="21" t="n"/>
+      <c r="AC53" s="21" t="n"/>
+      <c r="AD53" s="22" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="23" t="n"/>
+      <c r="B54" s="24" t="n"/>
+      <c r="C54" s="24" t="n"/>
+      <c r="D54" s="24" t="n"/>
+      <c r="E54" s="24" t="n"/>
+      <c r="F54" s="25" t="n"/>
+      <c r="I54" s="23" t="n"/>
+      <c r="J54" s="24" t="n"/>
+      <c r="K54" s="24" t="n"/>
+      <c r="L54" s="24" t="n"/>
+      <c r="M54" s="24" t="n"/>
+      <c r="N54" s="25" t="n"/>
+      <c r="Q54" s="23" t="n"/>
+      <c r="R54" s="24" t="n"/>
+      <c r="S54" s="24" t="n"/>
+      <c r="T54" s="24" t="n"/>
+      <c r="U54" s="24" t="n"/>
+      <c r="V54" s="25" t="n"/>
+      <c r="Y54" s="23" t="n"/>
+      <c r="Z54" s="24" t="n"/>
+      <c r="AA54" s="24" t="n"/>
+      <c r="AB54" s="24" t="n"/>
+      <c r="AC54" s="24" t="n"/>
+      <c r="AD54" s="25" t="n"/>
+    </row>
+    <row r="55">
+      <c r="B55" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C55" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D55" s="28" t="n">
+        <v>0.4340277777777778</v>
+      </c>
+      <c r="J55" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K55" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="L55" s="28" t="n">
+        <v>0.4340277777777778</v>
+      </c>
+      <c r="R55" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S55" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="T55" s="28" t="n">
+        <v>0.4340277777777778</v>
+      </c>
+      <c r="Z55" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA55" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB55" s="28" t="n">
+        <v>0.4340277777777778</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Static Shock</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="n"/>
+      <c r="C56" s="11" t="n"/>
+      <c r="D56" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 2</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="n"/>
+      <c r="F56" s="11" t="n"/>
+      <c r="I56" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Black Panther</t>
+        </is>
+      </c>
+      <c r="J56" s="11" t="n"/>
+      <c r="K56" s="11" t="n"/>
+      <c r="L56" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="M56" s="11" t="n"/>
+      <c r="N56" s="11" t="n"/>
+      <c r="Q56" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Boondocks</t>
+        </is>
+      </c>
+      <c r="R56" s="11" t="n"/>
+      <c r="S56" s="11" t="n"/>
+      <c r="T56" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="U56" s="11" t="n"/>
+      <c r="V56" s="11" t="n"/>
+      <c r="Y56" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Fresh Prince</t>
+        </is>
+      </c>
+      <c r="Z56" s="11" t="n"/>
+      <c r="AA56" s="11" t="n"/>
+      <c r="AB56" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 2</t>
+        </is>
+      </c>
+      <c r="AC56" s="11" t="n"/>
+      <c r="AD56" s="11" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="31" t="inlineStr">
+        <is>
+          <t>Proud Family</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n"/>
+      <c r="C57" s="11" t="n"/>
+      <c r="D57" s="31" t="inlineStr">
+        <is>
+          <t>That's So Raven</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="n"/>
+      <c r="F57" s="11" t="n"/>
+      <c r="I57" s="31" t="inlineStr">
+        <is>
+          <t>Abbott Elementary</t>
+        </is>
+      </c>
+      <c r="J57" s="11" t="n"/>
+      <c r="K57" s="11" t="n"/>
+      <c r="L57" s="31" t="inlineStr">
+        <is>
+          <t>The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="M57" s="11" t="n"/>
+      <c r="N57" s="11" t="n"/>
+      <c r="Q57" s="31" t="inlineStr">
+        <is>
+          <t>Smart Guy</t>
+        </is>
+      </c>
+      <c r="R57" s="11" t="n"/>
+      <c r="S57" s="11" t="n"/>
+      <c r="T57" s="31" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="U57" s="11" t="n"/>
+      <c r="V57" s="11" t="n"/>
+      <c r="Y57" s="31" t="inlineStr">
+        <is>
+          <t>The Parkers</t>
+        </is>
+      </c>
+      <c r="Z57" s="11" t="n"/>
+      <c r="AA57" s="11" t="n"/>
+      <c r="AB57" s="31" t="inlineStr">
+        <is>
+          <t>The Incredibles</t>
+        </is>
+      </c>
+      <c r="AC57" s="11" t="n"/>
+      <c r="AD57" s="11" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="n"/>
+      <c r="C58" s="11" t="n"/>
+      <c r="D58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="n"/>
+      <c r="F58" s="11" t="n"/>
+      <c r="I58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J58" s="11" t="n"/>
+      <c r="K58" s="11" t="n"/>
+      <c r="L58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M58" s="11" t="n"/>
+      <c r="N58" s="11" t="n"/>
+      <c r="Q58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R58" s="11" t="n"/>
+      <c r="S58" s="11" t="n"/>
+      <c r="T58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U58" s="11" t="n"/>
+      <c r="V58" s="11" t="n"/>
+      <c r="Y58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z58" s="11" t="n"/>
+      <c r="AA58" s="11" t="n"/>
+      <c r="AB58" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC58" s="11" t="n"/>
+      <c r="AD58" s="11" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="n"/>
+      <c r="B59" s="11" t="n"/>
+      <c r="C59" s="11" t="n"/>
+      <c r="D59" s="11" t="n"/>
+      <c r="E59" s="11" t="n"/>
+      <c r="F59" s="11" t="n"/>
+      <c r="I59" s="11" t="n"/>
+      <c r="J59" s="11" t="n"/>
+      <c r="K59" s="11" t="n"/>
+      <c r="L59" s="11" t="n"/>
+      <c r="M59" s="11" t="n"/>
+      <c r="N59" s="11" t="n"/>
+      <c r="Q59" s="11" t="n"/>
+      <c r="R59" s="11" t="n"/>
+      <c r="S59" s="11" t="n"/>
+      <c r="T59" s="11" t="n"/>
+      <c r="U59" s="11" t="n"/>
+      <c r="V59" s="11" t="n"/>
+      <c r="Y59" s="11" t="n"/>
+      <c r="Z59" s="11" t="n"/>
+      <c r="AA59" s="11" t="n"/>
+      <c r="AB59" s="11" t="n"/>
+      <c r="AC59" s="11" t="n"/>
+      <c r="AD59" s="11" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="n"/>
+      <c r="B60" s="11" t="n"/>
+      <c r="C60" s="11" t="n"/>
+      <c r="D60" s="11" t="n"/>
+      <c r="E60" s="11" t="n"/>
+      <c r="F60" s="11" t="n"/>
+      <c r="I60" s="11" t="n"/>
+      <c r="J60" s="11" t="n"/>
+      <c r="K60" s="11" t="n"/>
+      <c r="L60" s="11" t="n"/>
+      <c r="M60" s="11" t="n"/>
+      <c r="N60" s="11" t="n"/>
+      <c r="Q60" s="11" t="n"/>
+      <c r="R60" s="11" t="n"/>
+      <c r="S60" s="11" t="n"/>
+      <c r="T60" s="11" t="n"/>
+      <c r="U60" s="11" t="n"/>
+      <c r="V60" s="11" t="n"/>
+      <c r="Y60" s="11" t="n"/>
+      <c r="Z60" s="11" t="n"/>
+      <c r="AA60" s="11" t="n"/>
+      <c r="AB60" s="11" t="n"/>
+      <c r="AC60" s="11" t="n"/>
+      <c r="AD60" s="11" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="n"/>
+      <c r="B61" s="11" t="n"/>
+      <c r="C61" s="11" t="n"/>
+      <c r="D61" s="11" t="n"/>
+      <c r="E61" s="11" t="n"/>
+      <c r="F61" s="11" t="n"/>
+      <c r="I61" s="11" t="n"/>
+      <c r="J61" s="11" t="n"/>
+      <c r="K61" s="11" t="n"/>
+      <c r="L61" s="11" t="n"/>
+      <c r="M61" s="11" t="n"/>
+      <c r="N61" s="11" t="n"/>
+      <c r="Q61" s="11" t="n"/>
+      <c r="R61" s="11" t="n"/>
+      <c r="S61" s="11" t="n"/>
+      <c r="T61" s="11" t="n"/>
+      <c r="U61" s="11" t="n"/>
+      <c r="V61" s="11" t="n"/>
+      <c r="Y61" s="11" t="n"/>
+      <c r="Z61" s="11" t="n"/>
+      <c r="AA61" s="11" t="n"/>
+      <c r="AB61" s="11" t="n"/>
+      <c r="AC61" s="11" t="n"/>
+      <c r="AD61" s="11" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n"/>
+      <c r="C62" s="11" t="n"/>
+      <c r="D62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 4</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="n"/>
+      <c r="F62" s="11" t="n"/>
+      <c r="I62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Court 1</t>
+        </is>
+      </c>
+      <c r="J62" s="11" t="n"/>
+      <c r="K62" s="11" t="n"/>
+      <c r="L62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 1</t>
+        </is>
+      </c>
+      <c r="M62" s="11" t="n"/>
+      <c r="N62" s="11" t="n"/>
+      <c r="Q62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R62" s="11" t="n"/>
+      <c r="S62" s="11" t="n"/>
+      <c r="T62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 3</t>
+        </is>
+      </c>
+      <c r="U62" s="11" t="n"/>
+      <c r="V62" s="11" t="n"/>
+      <c r="Y62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Court 1</t>
+        </is>
+      </c>
+      <c r="Z62" s="11" t="n"/>
+      <c r="AA62" s="11" t="n"/>
+      <c r="AB62" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="AC62" s="11" t="n"/>
+      <c r="AD62" s="11" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n"/>
+      <c r="C63" s="11" t="n"/>
+      <c r="D63" s="11" t="n"/>
+      <c r="E63" s="11" t="n"/>
+      <c r="F63" s="11" t="n"/>
+      <c r="I63" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J63" s="11" t="n"/>
+      <c r="K63" s="11" t="n"/>
+      <c r="L63" s="11" t="n"/>
+      <c r="M63" s="11" t="n"/>
+      <c r="N63" s="11" t="n"/>
+      <c r="Q63" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R63" s="11" t="n"/>
+      <c r="S63" s="11" t="n"/>
+      <c r="T63" s="11" t="n"/>
+      <c r="U63" s="11" t="n"/>
+      <c r="V63" s="11" t="n"/>
+      <c r="Y63" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z63" s="11" t="n"/>
+      <c r="AA63" s="11" t="n"/>
+      <c r="AB63" s="11" t="n"/>
+      <c r="AC63" s="11" t="n"/>
+      <c r="AD63" s="11" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n"/>
+      <c r="C64" s="11" t="n"/>
+      <c r="D64" s="11" t="n"/>
+      <c r="E64" s="11" t="n"/>
+      <c r="F64" s="11" t="n"/>
+      <c r="I64" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J64" s="11" t="n"/>
+      <c r="K64" s="11" t="n"/>
+      <c r="L64" s="11" t="n"/>
+      <c r="M64" s="11" t="n"/>
+      <c r="N64" s="11" t="n"/>
+      <c r="Q64" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R64" s="11" t="n"/>
+      <c r="S64" s="11" t="n"/>
+      <c r="T64" s="11" t="n"/>
+      <c r="U64" s="11" t="n"/>
+      <c r="V64" s="11" t="n"/>
+      <c r="Y64" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z64" s="11" t="n"/>
+      <c r="AA64" s="11" t="n"/>
+      <c r="AB64" s="11" t="n"/>
+      <c r="AC64" s="11" t="n"/>
+      <c r="AD64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n"/>
+      <c r="C65" s="11" t="n"/>
+      <c r="D65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E65" s="11" t="n"/>
+      <c r="F65" s="11" t="n"/>
+      <c r="I65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J65" s="11" t="n"/>
+      <c r="K65" s="11" t="n"/>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M65" s="11" t="n"/>
+      <c r="N65" s="11" t="n"/>
+      <c r="Q65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R65" s="11" t="n"/>
+      <c r="S65" s="11" t="n"/>
+      <c r="T65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U65" s="11" t="n"/>
+      <c r="V65" s="11" t="n"/>
+      <c r="Y65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z65" s="11" t="n"/>
+      <c r="AA65" s="11" t="n"/>
+      <c r="AB65" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC65" s="11" t="n"/>
+      <c r="AD65" s="11" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="n"/>
+      <c r="B66" s="11" t="n"/>
+      <c r="C66" s="11" t="n"/>
+      <c r="D66" s="11" t="n"/>
+      <c r="E66" s="11" t="n"/>
+      <c r="F66" s="11" t="n"/>
+      <c r="I66" s="11" t="n"/>
+      <c r="J66" s="11" t="n"/>
+      <c r="K66" s="11" t="n"/>
+      <c r="L66" s="11" t="n"/>
+      <c r="M66" s="11" t="n"/>
+      <c r="N66" s="11" t="n"/>
+      <c r="Q66" s="11" t="n"/>
+      <c r="R66" s="11" t="n"/>
+      <c r="S66" s="11" t="n"/>
+      <c r="T66" s="11" t="n"/>
+      <c r="U66" s="11" t="n"/>
+      <c r="V66" s="11" t="n"/>
+      <c r="Y66" s="11" t="n"/>
+      <c r="Z66" s="11" t="n"/>
+      <c r="AA66" s="11" t="n"/>
+      <c r="AB66" s="11" t="n"/>
+      <c r="AC66" s="11" t="n"/>
+      <c r="AD66" s="11" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B67" s="35" t="n"/>
+      <c r="C67" s="35" t="n"/>
+      <c r="D67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E67" s="35" t="n"/>
+      <c r="F67" s="35" t="n"/>
+      <c r="I67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J67" s="35" t="n"/>
+      <c r="K67" s="35" t="n"/>
+      <c r="L67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M67" s="35" t="n"/>
+      <c r="N67" s="35" t="n"/>
+      <c r="Q67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R67" s="35" t="n"/>
+      <c r="S67" s="35" t="n"/>
+      <c r="T67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U67" s="35" t="n"/>
+      <c r="V67" s="35" t="n"/>
+      <c r="Y67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z67" s="35" t="n"/>
+      <c r="AA67" s="35" t="n"/>
+      <c r="AB67" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC67" s="35" t="n"/>
+      <c r="AD67" s="35" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="35" t="n"/>
+      <c r="B68" s="35" t="n"/>
+      <c r="C68" s="35" t="n"/>
+      <c r="D68" s="35" t="n"/>
+      <c r="E68" s="35" t="n"/>
+      <c r="F68" s="35" t="n"/>
+      <c r="I68" s="35" t="n"/>
+      <c r="J68" s="35" t="n"/>
+      <c r="K68" s="35" t="n"/>
+      <c r="L68" s="35" t="n"/>
+      <c r="M68" s="35" t="n"/>
+      <c r="N68" s="35" t="n"/>
+      <c r="Q68" s="35" t="n"/>
+      <c r="R68" s="35" t="n"/>
+      <c r="S68" s="35" t="n"/>
+      <c r="T68" s="35" t="n"/>
+      <c r="U68" s="35" t="n"/>
+      <c r="V68" s="35" t="n"/>
+      <c r="Y68" s="35" t="n"/>
+      <c r="Z68" s="35" t="n"/>
+      <c r="AA68" s="35" t="n"/>
+      <c r="AB68" s="35" t="n"/>
+      <c r="AC68" s="35" t="n"/>
+      <c r="AD68" s="35" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B71" s="21" t="n"/>
+      <c r="C71" s="21" t="n"/>
+      <c r="D71" s="21" t="n"/>
+      <c r="E71" s="21" t="n"/>
+      <c r="F71" s="22" t="n"/>
+      <c r="I71" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J71" s="21" t="n"/>
+      <c r="K71" s="21" t="n"/>
+      <c r="L71" s="21" t="n"/>
+      <c r="M71" s="21" t="n"/>
+      <c r="N71" s="22" t="n"/>
+      <c r="Q71" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R71" s="21" t="n"/>
+      <c r="S71" s="21" t="n"/>
+      <c r="T71" s="21" t="n"/>
+      <c r="U71" s="21" t="n"/>
+      <c r="V71" s="22" t="n"/>
+      <c r="Y71" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z71" s="21" t="n"/>
+      <c r="AA71" s="21" t="n"/>
+      <c r="AB71" s="21" t="n"/>
+      <c r="AC71" s="21" t="n"/>
+      <c r="AD71" s="22" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="23" t="n"/>
+      <c r="B72" s="24" t="n"/>
+      <c r="C72" s="24" t="n"/>
+      <c r="D72" s="24" t="n"/>
+      <c r="E72" s="24" t="n"/>
+      <c r="F72" s="25" t="n"/>
+      <c r="I72" s="23" t="n"/>
+      <c r="J72" s="24" t="n"/>
+      <c r="K72" s="24" t="n"/>
+      <c r="L72" s="24" t="n"/>
+      <c r="M72" s="24" t="n"/>
+      <c r="N72" s="25" t="n"/>
+      <c r="Q72" s="23" t="n"/>
+      <c r="R72" s="24" t="n"/>
+      <c r="S72" s="24" t="n"/>
+      <c r="T72" s="24" t="n"/>
+      <c r="U72" s="24" t="n"/>
+      <c r="V72" s="25" t="n"/>
+      <c r="Y72" s="23" t="n"/>
+      <c r="Z72" s="24" t="n"/>
+      <c r="AA72" s="24" t="n"/>
+      <c r="AB72" s="24" t="n"/>
+      <c r="AC72" s="24" t="n"/>
+      <c r="AD72" s="25" t="n"/>
+    </row>
+    <row r="73">
+      <c r="B73" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C73" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D73" s="28" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="J73" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K73" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="L73" s="28" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="R73" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S73" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" s="28" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+      <c r="Z73" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA73" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB73" s="28" t="n">
+        <v>0.4513888888888889</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n"/>
+      <c r="C74" s="11" t="n"/>
+      <c r="D74" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 2</t>
+        </is>
+      </c>
+      <c r="E74" s="11" t="n"/>
+      <c r="F74" s="11" t="n"/>
+      <c r="I74" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Family Matters</t>
+        </is>
+      </c>
+      <c r="J74" s="11" t="n"/>
+      <c r="K74" s="11" t="n"/>
+      <c r="L74" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="M74" s="11" t="n"/>
+      <c r="N74" s="11" t="n"/>
+      <c r="Q74" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Sister Sister</t>
+        </is>
+      </c>
+      <c r="R74" s="11" t="n"/>
+      <c r="S74" s="11" t="n"/>
+      <c r="T74" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="U74" s="11" t="n"/>
+      <c r="V74" s="11" t="n"/>
+      <c r="Y74" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Fillmore</t>
+        </is>
+      </c>
+      <c r="Z74" s="11" t="n"/>
+      <c r="AA74" s="11" t="n"/>
+      <c r="AB74" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="AC74" s="11" t="n"/>
+      <c r="AD74" s="11" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="31" t="inlineStr">
+        <is>
+          <t>The Parkers</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n"/>
+      <c r="C75" s="11" t="n"/>
+      <c r="D75" s="31" t="inlineStr">
+        <is>
+          <t>Abbott Elementary</t>
+        </is>
+      </c>
+      <c r="E75" s="11" t="n"/>
+      <c r="F75" s="11" t="n"/>
+      <c r="I75" s="31" t="inlineStr">
+        <is>
+          <t>Fresh Prince</t>
+        </is>
+      </c>
+      <c r="J75" s="11" t="n"/>
+      <c r="K75" s="11" t="n"/>
+      <c r="L75" s="31" t="inlineStr">
+        <is>
+          <t>Static Shock</t>
+        </is>
+      </c>
+      <c r="M75" s="11" t="n"/>
+      <c r="N75" s="11" t="n"/>
+      <c r="Q75" s="31" t="inlineStr">
+        <is>
+          <t>The Boondocks</t>
+        </is>
+      </c>
+      <c r="R75" s="11" t="n"/>
+      <c r="S75" s="11" t="n"/>
+      <c r="T75" s="31" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="U75" s="11" t="n"/>
+      <c r="V75" s="11" t="n"/>
+      <c r="Y75" s="31" t="inlineStr">
+        <is>
+          <t>Black Panther</t>
+        </is>
+      </c>
+      <c r="Z75" s="11" t="n"/>
+      <c r="AA75" s="11" t="n"/>
+      <c r="AB75" s="31" t="inlineStr">
+        <is>
+          <t>That's So Raven</t>
+        </is>
+      </c>
+      <c r="AC75" s="11" t="n"/>
+      <c r="AD75" s="11" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n"/>
+      <c r="C76" s="11" t="n"/>
+      <c r="D76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E76" s="11" t="n"/>
+      <c r="F76" s="11" t="n"/>
+      <c r="I76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J76" s="11" t="n"/>
+      <c r="K76" s="11" t="n"/>
+      <c r="L76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M76" s="11" t="n"/>
+      <c r="N76" s="11" t="n"/>
+      <c r="Q76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R76" s="11" t="n"/>
+      <c r="S76" s="11" t="n"/>
+      <c r="T76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U76" s="11" t="n"/>
+      <c r="V76" s="11" t="n"/>
+      <c r="Y76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z76" s="11" t="n"/>
+      <c r="AA76" s="11" t="n"/>
+      <c r="AB76" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC76" s="11" t="n"/>
+      <c r="AD76" s="11" t="n"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="n"/>
+      <c r="B77" s="11" t="n"/>
+      <c r="C77" s="11" t="n"/>
+      <c r="D77" s="11" t="n"/>
+      <c r="E77" s="11" t="n"/>
+      <c r="F77" s="11" t="n"/>
+      <c r="I77" s="11" t="n"/>
+      <c r="J77" s="11" t="n"/>
+      <c r="K77" s="11" t="n"/>
+      <c r="L77" s="11" t="n"/>
+      <c r="M77" s="11" t="n"/>
+      <c r="N77" s="11" t="n"/>
+      <c r="Q77" s="11" t="n"/>
+      <c r="R77" s="11" t="n"/>
+      <c r="S77" s="11" t="n"/>
+      <c r="T77" s="11" t="n"/>
+      <c r="U77" s="11" t="n"/>
+      <c r="V77" s="11" t="n"/>
+      <c r="Y77" s="11" t="n"/>
+      <c r="Z77" s="11" t="n"/>
+      <c r="AA77" s="11" t="n"/>
+      <c r="AB77" s="11" t="n"/>
+      <c r="AC77" s="11" t="n"/>
+      <c r="AD77" s="11" t="n"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="n"/>
+      <c r="B78" s="11" t="n"/>
+      <c r="C78" s="11" t="n"/>
+      <c r="D78" s="11" t="n"/>
+      <c r="E78" s="11" t="n"/>
+      <c r="F78" s="11" t="n"/>
+      <c r="I78" s="11" t="n"/>
+      <c r="J78" s="11" t="n"/>
+      <c r="K78" s="11" t="n"/>
+      <c r="L78" s="11" t="n"/>
+      <c r="M78" s="11" t="n"/>
+      <c r="N78" s="11" t="n"/>
+      <c r="Q78" s="11" t="n"/>
+      <c r="R78" s="11" t="n"/>
+      <c r="S78" s="11" t="n"/>
+      <c r="T78" s="11" t="n"/>
+      <c r="U78" s="11" t="n"/>
+      <c r="V78" s="11" t="n"/>
+      <c r="Y78" s="11" t="n"/>
+      <c r="Z78" s="11" t="n"/>
+      <c r="AA78" s="11" t="n"/>
+      <c r="AB78" s="11" t="n"/>
+      <c r="AC78" s="11" t="n"/>
+      <c r="AD78" s="11" t="n"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="n"/>
+      <c r="B79" s="11" t="n"/>
+      <c r="C79" s="11" t="n"/>
+      <c r="D79" s="11" t="n"/>
+      <c r="E79" s="11" t="n"/>
+      <c r="F79" s="11" t="n"/>
+      <c r="I79" s="11" t="n"/>
+      <c r="J79" s="11" t="n"/>
+      <c r="K79" s="11" t="n"/>
+      <c r="L79" s="11" t="n"/>
+      <c r="M79" s="11" t="n"/>
+      <c r="N79" s="11" t="n"/>
+      <c r="Q79" s="11" t="n"/>
+      <c r="R79" s="11" t="n"/>
+      <c r="S79" s="11" t="n"/>
+      <c r="T79" s="11" t="n"/>
+      <c r="U79" s="11" t="n"/>
+      <c r="V79" s="11" t="n"/>
+      <c r="Y79" s="11" t="n"/>
+      <c r="Z79" s="11" t="n"/>
+      <c r="AA79" s="11" t="n"/>
+      <c r="AB79" s="11" t="n"/>
+      <c r="AC79" s="11" t="n"/>
+      <c r="AD79" s="11" t="n"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 3</t>
+        </is>
+      </c>
+      <c r="B80" s="11" t="n"/>
+      <c r="C80" s="11" t="n"/>
+      <c r="D80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="E80" s="11" t="n"/>
+      <c r="F80" s="11" t="n"/>
+      <c r="I80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="J80" s="11" t="n"/>
+      <c r="K80" s="11" t="n"/>
+      <c r="L80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 1</t>
+        </is>
+      </c>
+      <c r="M80" s="11" t="n"/>
+      <c r="N80" s="11" t="n"/>
+      <c r="Q80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R80" s="11" t="n"/>
+      <c r="S80" s="11" t="n"/>
+      <c r="T80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 2</t>
+        </is>
+      </c>
+      <c r="U80" s="11" t="n"/>
+      <c r="V80" s="11" t="n"/>
+      <c r="Y80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="Z80" s="11" t="n"/>
+      <c r="AA80" s="11" t="n"/>
+      <c r="AB80" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 4</t>
+        </is>
+      </c>
+      <c r="AC80" s="11" t="n"/>
+      <c r="AD80" s="11" t="n"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n"/>
+      <c r="C81" s="11" t="n"/>
+      <c r="D81" s="11" t="n"/>
+      <c r="E81" s="11" t="n"/>
+      <c r="F81" s="11" t="n"/>
+      <c r="I81" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J81" s="11" t="n"/>
+      <c r="K81" s="11" t="n"/>
+      <c r="L81" s="11" t="n"/>
+      <c r="M81" s="11" t="n"/>
+      <c r="N81" s="11" t="n"/>
+      <c r="Q81" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R81" s="11" t="n"/>
+      <c r="S81" s="11" t="n"/>
+      <c r="T81" s="11" t="n"/>
+      <c r="U81" s="11" t="n"/>
+      <c r="V81" s="11" t="n"/>
+      <c r="Y81" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z81" s="11" t="n"/>
+      <c r="AA81" s="11" t="n"/>
+      <c r="AB81" s="11" t="n"/>
+      <c r="AC81" s="11" t="n"/>
+      <c r="AD81" s="11" t="n"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B82" s="11" t="n"/>
+      <c r="C82" s="11" t="n"/>
+      <c r="D82" s="11" t="n"/>
+      <c r="E82" s="11" t="n"/>
+      <c r="F82" s="11" t="n"/>
+      <c r="I82" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J82" s="11" t="n"/>
+      <c r="K82" s="11" t="n"/>
+      <c r="L82" s="11" t="n"/>
+      <c r="M82" s="11" t="n"/>
+      <c r="N82" s="11" t="n"/>
+      <c r="Q82" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R82" s="11" t="n"/>
+      <c r="S82" s="11" t="n"/>
+      <c r="T82" s="11" t="n"/>
+      <c r="U82" s="11" t="n"/>
+      <c r="V82" s="11" t="n"/>
+      <c r="Y82" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z82" s="11" t="n"/>
+      <c r="AA82" s="11" t="n"/>
+      <c r="AB82" s="11" t="n"/>
+      <c r="AC82" s="11" t="n"/>
+      <c r="AD82" s="11" t="n"/>
+    </row>
+    <row r="83">
+      <c r="A83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B83" s="11" t="n"/>
+      <c r="C83" s="11" t="n"/>
+      <c r="D83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E83" s="11" t="n"/>
+      <c r="F83" s="11" t="n"/>
+      <c r="I83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J83" s="11" t="n"/>
+      <c r="K83" s="11" t="n"/>
+      <c r="L83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M83" s="11" t="n"/>
+      <c r="N83" s="11" t="n"/>
+      <c r="Q83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R83" s="11" t="n"/>
+      <c r="S83" s="11" t="n"/>
+      <c r="T83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U83" s="11" t="n"/>
+      <c r="V83" s="11" t="n"/>
+      <c r="Y83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z83" s="11" t="n"/>
+      <c r="AA83" s="11" t="n"/>
+      <c r="AB83" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC83" s="11" t="n"/>
+      <c r="AD83" s="11" t="n"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="n"/>
+      <c r="B84" s="11" t="n"/>
+      <c r="C84" s="11" t="n"/>
+      <c r="D84" s="11" t="n"/>
+      <c r="E84" s="11" t="n"/>
+      <c r="F84" s="11" t="n"/>
+      <c r="I84" s="11" t="n"/>
+      <c r="J84" s="11" t="n"/>
+      <c r="K84" s="11" t="n"/>
+      <c r="L84" s="11" t="n"/>
+      <c r="M84" s="11" t="n"/>
+      <c r="N84" s="11" t="n"/>
+      <c r="Q84" s="11" t="n"/>
+      <c r="R84" s="11" t="n"/>
+      <c r="S84" s="11" t="n"/>
+      <c r="T84" s="11" t="n"/>
+      <c r="U84" s="11" t="n"/>
+      <c r="V84" s="11" t="n"/>
+      <c r="Y84" s="11" t="n"/>
+      <c r="Z84" s="11" t="n"/>
+      <c r="AA84" s="11" t="n"/>
+      <c r="AB84" s="11" t="n"/>
+      <c r="AC84" s="11" t="n"/>
+      <c r="AD84" s="11" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B85" s="35" t="n"/>
+      <c r="C85" s="35" t="n"/>
+      <c r="D85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E85" s="35" t="n"/>
+      <c r="F85" s="35" t="n"/>
+      <c r="I85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J85" s="35" t="n"/>
+      <c r="K85" s="35" t="n"/>
+      <c r="L85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M85" s="35" t="n"/>
+      <c r="N85" s="35" t="n"/>
+      <c r="Q85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R85" s="35" t="n"/>
+      <c r="S85" s="35" t="n"/>
+      <c r="T85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U85" s="35" t="n"/>
+      <c r="V85" s="35" t="n"/>
+      <c r="Y85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z85" s="35" t="n"/>
+      <c r="AA85" s="35" t="n"/>
+      <c r="AB85" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC85" s="35" t="n"/>
+      <c r="AD85" s="35" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="35" t="n"/>
+      <c r="B86" s="35" t="n"/>
+      <c r="C86" s="35" t="n"/>
+      <c r="D86" s="35" t="n"/>
+      <c r="E86" s="35" t="n"/>
+      <c r="F86" s="35" t="n"/>
+      <c r="I86" s="35" t="n"/>
+      <c r="J86" s="35" t="n"/>
+      <c r="K86" s="35" t="n"/>
+      <c r="L86" s="35" t="n"/>
+      <c r="M86" s="35" t="n"/>
+      <c r="N86" s="35" t="n"/>
+      <c r="Q86" s="35" t="n"/>
+      <c r="R86" s="35" t="n"/>
+      <c r="S86" s="35" t="n"/>
+      <c r="T86" s="35" t="n"/>
+      <c r="U86" s="35" t="n"/>
+      <c r="V86" s="35" t="n"/>
+      <c r="Y86" s="35" t="n"/>
+      <c r="Z86" s="35" t="n"/>
+      <c r="AA86" s="35" t="n"/>
+      <c r="AB86" s="35" t="n"/>
+      <c r="AC86" s="35" t="n"/>
+      <c r="AD86" s="35" t="n"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B88" s="21" t="n"/>
+      <c r="C88" s="21" t="n"/>
+      <c r="D88" s="21" t="n"/>
+      <c r="E88" s="21" t="n"/>
+      <c r="F88" s="22" t="n"/>
+      <c r="I88" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J88" s="21" t="n"/>
+      <c r="K88" s="21" t="n"/>
+      <c r="L88" s="21" t="n"/>
+      <c r="M88" s="21" t="n"/>
+      <c r="N88" s="22" t="n"/>
+      <c r="Q88" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R88" s="21" t="n"/>
+      <c r="S88" s="21" t="n"/>
+      <c r="T88" s="21" t="n"/>
+      <c r="U88" s="21" t="n"/>
+      <c r="V88" s="22" t="n"/>
+      <c r="Y88" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z88" s="21" t="n"/>
+      <c r="AA88" s="21" t="n"/>
+      <c r="AB88" s="21" t="n"/>
+      <c r="AC88" s="21" t="n"/>
+      <c r="AD88" s="22" t="n"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="23" t="n"/>
+      <c r="B89" s="24" t="n"/>
+      <c r="C89" s="24" t="n"/>
+      <c r="D89" s="24" t="n"/>
+      <c r="E89" s="24" t="n"/>
+      <c r="F89" s="25" t="n"/>
+      <c r="I89" s="23" t="n"/>
+      <c r="J89" s="24" t="n"/>
+      <c r="K89" s="24" t="n"/>
+      <c r="L89" s="24" t="n"/>
+      <c r="M89" s="24" t="n"/>
+      <c r="N89" s="25" t="n"/>
+      <c r="Q89" s="23" t="n"/>
+      <c r="R89" s="24" t="n"/>
+      <c r="S89" s="24" t="n"/>
+      <c r="T89" s="24" t="n"/>
+      <c r="U89" s="24" t="n"/>
+      <c r="V89" s="25" t="n"/>
+      <c r="Y89" s="23" t="n"/>
+      <c r="Z89" s="24" t="n"/>
+      <c r="AA89" s="24" t="n"/>
+      <c r="AB89" s="24" t="n"/>
+      <c r="AC89" s="24" t="n"/>
+      <c r="AD89" s="25" t="n"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C90" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="D90" s="28" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="J90" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K90" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="L90" s="28" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="R90" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S90" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="T90" s="28" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="Z90" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA90" s="27" t="n">
+        <v>6</v>
+      </c>
+      <c r="AB90" s="28" t="n">
+        <v>0.46875</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Static Shock</t>
+        </is>
+      </c>
+      <c r="B91" s="11" t="n"/>
+      <c r="C91" s="11" t="n"/>
+      <c r="D91" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="E91" s="11" t="n"/>
+      <c r="F91" s="11" t="n"/>
+      <c r="I91" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Martin</t>
+        </is>
+      </c>
+      <c r="J91" s="11" t="n"/>
+      <c r="K91" s="11" t="n"/>
+      <c r="L91" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 1</t>
+        </is>
+      </c>
+      <c r="M91" s="11" t="n"/>
+      <c r="N91" s="11" t="n"/>
+      <c r="Q91" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Parkers</t>
+        </is>
+      </c>
+      <c r="R91" s="11" t="n"/>
+      <c r="S91" s="11" t="n"/>
+      <c r="T91" s="30" t="inlineStr">
+        <is>
+          <t>Next: OFF</t>
+        </is>
+      </c>
+      <c r="U91" s="11" t="n"/>
+      <c r="V91" s="11" t="n"/>
+      <c r="Y91" s="30" t="inlineStr">
+        <is>
+          <t>Ref: That's So Raven</t>
+        </is>
+      </c>
+      <c r="Z91" s="11" t="n"/>
+      <c r="AA91" s="11" t="n"/>
+      <c r="AB91" s="30" t="inlineStr">
+        <is>
+          <t>Next: Ref Court 3</t>
+        </is>
+      </c>
+      <c r="AC91" s="11" t="n"/>
+      <c r="AD91" s="11" t="n"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="31" t="inlineStr">
+        <is>
+          <t>Smart Guy</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="n"/>
+      <c r="C92" s="11" t="n"/>
+      <c r="D92" s="31" t="inlineStr">
+        <is>
+          <t>Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="E92" s="11" t="n"/>
+      <c r="F92" s="11" t="n"/>
+      <c r="I92" s="31" t="inlineStr">
+        <is>
+          <t>The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="J92" s="11" t="n"/>
+      <c r="K92" s="11" t="n"/>
+      <c r="L92" s="31" t="inlineStr">
+        <is>
+          <t>The Incredibles</t>
+        </is>
+      </c>
+      <c r="M92" s="11" t="n"/>
+      <c r="N92" s="11" t="n"/>
+      <c r="Q92" s="31" t="inlineStr">
+        <is>
+          <t>Family Matters</t>
+        </is>
+      </c>
+      <c r="R92" s="11" t="n"/>
+      <c r="S92" s="11" t="n"/>
+      <c r="T92" s="31" t="inlineStr">
+        <is>
+          <t>Sister Sister</t>
+        </is>
+      </c>
+      <c r="U92" s="11" t="n"/>
+      <c r="V92" s="11" t="n"/>
+      <c r="Y92" s="31" t="inlineStr">
+        <is>
+          <t>Fillmore</t>
+        </is>
+      </c>
+      <c r="Z92" s="11" t="n"/>
+      <c r="AA92" s="11" t="n"/>
+      <c r="AB92" s="31" t="inlineStr">
+        <is>
+          <t>Proud Family</t>
+        </is>
+      </c>
+      <c r="AC92" s="11" t="n"/>
+      <c r="AD92" s="11" t="n"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B93" s="11" t="n"/>
+      <c r="C93" s="11" t="n"/>
+      <c r="D93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E93" s="11" t="n"/>
+      <c r="F93" s="11" t="n"/>
+      <c r="I93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J93" s="11" t="n"/>
+      <c r="K93" s="11" t="n"/>
+      <c r="L93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M93" s="11" t="n"/>
+      <c r="N93" s="11" t="n"/>
+      <c r="Q93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R93" s="11" t="n"/>
+      <c r="S93" s="11" t="n"/>
+      <c r="T93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U93" s="11" t="n"/>
+      <c r="V93" s="11" t="n"/>
+      <c r="Y93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z93" s="11" t="n"/>
+      <c r="AA93" s="11" t="n"/>
+      <c r="AB93" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC93" s="11" t="n"/>
+      <c r="AD93" s="11" t="n"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="11" t="n"/>
+      <c r="B94" s="11" t="n"/>
+      <c r="C94" s="11" t="n"/>
+      <c r="D94" s="11" t="n"/>
+      <c r="E94" s="11" t="n"/>
+      <c r="F94" s="11" t="n"/>
+      <c r="I94" s="11" t="n"/>
+      <c r="J94" s="11" t="n"/>
+      <c r="K94" s="11" t="n"/>
+      <c r="L94" s="11" t="n"/>
+      <c r="M94" s="11" t="n"/>
+      <c r="N94" s="11" t="n"/>
+      <c r="Q94" s="11" t="n"/>
+      <c r="R94" s="11" t="n"/>
+      <c r="S94" s="11" t="n"/>
+      <c r="T94" s="11" t="n"/>
+      <c r="U94" s="11" t="n"/>
+      <c r="V94" s="11" t="n"/>
+      <c r="Y94" s="11" t="n"/>
+      <c r="Z94" s="11" t="n"/>
+      <c r="AA94" s="11" t="n"/>
+      <c r="AB94" s="11" t="n"/>
+      <c r="AC94" s="11" t="n"/>
+      <c r="AD94" s="11" t="n"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="11" t="n"/>
+      <c r="B95" s="11" t="n"/>
+      <c r="C95" s="11" t="n"/>
+      <c r="D95" s="11" t="n"/>
+      <c r="E95" s="11" t="n"/>
+      <c r="F95" s="11" t="n"/>
+      <c r="I95" s="11" t="n"/>
+      <c r="J95" s="11" t="n"/>
+      <c r="K95" s="11" t="n"/>
+      <c r="L95" s="11" t="n"/>
+      <c r="M95" s="11" t="n"/>
+      <c r="N95" s="11" t="n"/>
+      <c r="Q95" s="11" t="n"/>
+      <c r="R95" s="11" t="n"/>
+      <c r="S95" s="11" t="n"/>
+      <c r="T95" s="11" t="n"/>
+      <c r="U95" s="11" t="n"/>
+      <c r="V95" s="11" t="n"/>
+      <c r="Y95" s="11" t="n"/>
+      <c r="Z95" s="11" t="n"/>
+      <c r="AA95" s="11" t="n"/>
+      <c r="AB95" s="11" t="n"/>
+      <c r="AC95" s="11" t="n"/>
+      <c r="AD95" s="11" t="n"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="11" t="n"/>
+      <c r="B96" s="11" t="n"/>
+      <c r="C96" s="11" t="n"/>
+      <c r="D96" s="11" t="n"/>
+      <c r="E96" s="11" t="n"/>
+      <c r="F96" s="11" t="n"/>
+      <c r="I96" s="11" t="n"/>
+      <c r="J96" s="11" t="n"/>
+      <c r="K96" s="11" t="n"/>
+      <c r="L96" s="11" t="n"/>
+      <c r="M96" s="11" t="n"/>
+      <c r="N96" s="11" t="n"/>
+      <c r="Q96" s="11" t="n"/>
+      <c r="R96" s="11" t="n"/>
+      <c r="S96" s="11" t="n"/>
+      <c r="T96" s="11" t="n"/>
+      <c r="U96" s="11" t="n"/>
+      <c r="V96" s="11" t="n"/>
+      <c r="Y96" s="11" t="n"/>
+      <c r="Z96" s="11" t="n"/>
+      <c r="AA96" s="11" t="n"/>
+      <c r="AB96" s="11" t="n"/>
+      <c r="AC96" s="11" t="n"/>
+      <c r="AD96" s="11" t="n"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 1</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="n"/>
+      <c r="C97" s="11" t="n"/>
+      <c r="D97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 3</t>
+        </is>
+      </c>
+      <c r="E97" s="11" t="n"/>
+      <c r="F97" s="11" t="n"/>
+      <c r="I97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Court 2</t>
+        </is>
+      </c>
+      <c r="J97" s="11" t="n"/>
+      <c r="K97" s="11" t="n"/>
+      <c r="L97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 4</t>
+        </is>
+      </c>
+      <c r="M97" s="11" t="n"/>
+      <c r="N97" s="11" t="n"/>
+      <c r="Q97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R97" s="11" t="n"/>
+      <c r="S97" s="11" t="n"/>
+      <c r="T97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 1</t>
+        </is>
+      </c>
+      <c r="U97" s="11" t="n"/>
+      <c r="V97" s="11" t="n"/>
+      <c r="Y97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Court 4</t>
+        </is>
+      </c>
+      <c r="Z97" s="11" t="n"/>
+      <c r="AA97" s="11" t="n"/>
+      <c r="AB97" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 2</t>
+        </is>
+      </c>
+      <c r="AC97" s="11" t="n"/>
+      <c r="AD97" s="11" t="n"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B98" s="11" t="n"/>
+      <c r="C98" s="11" t="n"/>
+      <c r="D98" s="11" t="n"/>
+      <c r="E98" s="11" t="n"/>
+      <c r="F98" s="11" t="n"/>
+      <c r="I98" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J98" s="11" t="n"/>
+      <c r="K98" s="11" t="n"/>
+      <c r="L98" s="11" t="n"/>
+      <c r="M98" s="11" t="n"/>
+      <c r="N98" s="11" t="n"/>
+      <c r="Q98" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R98" s="11" t="n"/>
+      <c r="S98" s="11" t="n"/>
+      <c r="T98" s="11" t="n"/>
+      <c r="U98" s="11" t="n"/>
+      <c r="V98" s="11" t="n"/>
+      <c r="Y98" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z98" s="11" t="n"/>
+      <c r="AA98" s="11" t="n"/>
+      <c r="AB98" s="11" t="n"/>
+      <c r="AC98" s="11" t="n"/>
+      <c r="AD98" s="11" t="n"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B99" s="11" t="n"/>
+      <c r="C99" s="11" t="n"/>
+      <c r="D99" s="11" t="n"/>
+      <c r="E99" s="11" t="n"/>
+      <c r="F99" s="11" t="n"/>
+      <c r="I99" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J99" s="11" t="n"/>
+      <c r="K99" s="11" t="n"/>
+      <c r="L99" s="11" t="n"/>
+      <c r="M99" s="11" t="n"/>
+      <c r="N99" s="11" t="n"/>
+      <c r="Q99" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R99" s="11" t="n"/>
+      <c r="S99" s="11" t="n"/>
+      <c r="T99" s="11" t="n"/>
+      <c r="U99" s="11" t="n"/>
+      <c r="V99" s="11" t="n"/>
+      <c r="Y99" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z99" s="11" t="n"/>
+      <c r="AA99" s="11" t="n"/>
+      <c r="AB99" s="11" t="n"/>
+      <c r="AC99" s="11" t="n"/>
+      <c r="AD99" s="11" t="n"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B100" s="11" t="n"/>
+      <c r="C100" s="11" t="n"/>
+      <c r="D100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E100" s="11" t="n"/>
+      <c r="F100" s="11" t="n"/>
+      <c r="I100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J100" s="11" t="n"/>
+      <c r="K100" s="11" t="n"/>
+      <c r="L100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M100" s="11" t="n"/>
+      <c r="N100" s="11" t="n"/>
+      <c r="Q100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R100" s="11" t="n"/>
+      <c r="S100" s="11" t="n"/>
+      <c r="T100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U100" s="11" t="n"/>
+      <c r="V100" s="11" t="n"/>
+      <c r="Y100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z100" s="11" t="n"/>
+      <c r="AA100" s="11" t="n"/>
+      <c r="AB100" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC100" s="11" t="n"/>
+      <c r="AD100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="n"/>
+      <c r="B101" s="11" t="n"/>
+      <c r="C101" s="11" t="n"/>
+      <c r="D101" s="11" t="n"/>
+      <c r="E101" s="11" t="n"/>
+      <c r="F101" s="11" t="n"/>
+      <c r="I101" s="11" t="n"/>
+      <c r="J101" s="11" t="n"/>
+      <c r="K101" s="11" t="n"/>
+      <c r="L101" s="11" t="n"/>
+      <c r="M101" s="11" t="n"/>
+      <c r="N101" s="11" t="n"/>
+      <c r="Q101" s="11" t="n"/>
+      <c r="R101" s="11" t="n"/>
+      <c r="S101" s="11" t="n"/>
+      <c r="T101" s="11" t="n"/>
+      <c r="U101" s="11" t="n"/>
+      <c r="V101" s="11" t="n"/>
+      <c r="Y101" s="11" t="n"/>
+      <c r="Z101" s="11" t="n"/>
+      <c r="AA101" s="11" t="n"/>
+      <c r="AB101" s="11" t="n"/>
+      <c r="AC101" s="11" t="n"/>
+      <c r="AD101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B102" s="35" t="n"/>
+      <c r="C102" s="35" t="n"/>
+      <c r="D102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E102" s="35" t="n"/>
+      <c r="F102" s="35" t="n"/>
+      <c r="I102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J102" s="35" t="n"/>
+      <c r="K102" s="35" t="n"/>
+      <c r="L102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M102" s="35" t="n"/>
+      <c r="N102" s="35" t="n"/>
+      <c r="Q102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R102" s="35" t="n"/>
+      <c r="S102" s="35" t="n"/>
+      <c r="T102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U102" s="35" t="n"/>
+      <c r="V102" s="35" t="n"/>
+      <c r="Y102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z102" s="35" t="n"/>
+      <c r="AA102" s="35" t="n"/>
+      <c r="AB102" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC102" s="35" t="n"/>
+      <c r="AD102" s="35" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" s="35" t="n"/>
+      <c r="B103" s="35" t="n"/>
+      <c r="C103" s="35" t="n"/>
+      <c r="D103" s="35" t="n"/>
+      <c r="E103" s="35" t="n"/>
+      <c r="F103" s="35" t="n"/>
+      <c r="I103" s="35" t="n"/>
+      <c r="J103" s="35" t="n"/>
+      <c r="K103" s="35" t="n"/>
+      <c r="L103" s="35" t="n"/>
+      <c r="M103" s="35" t="n"/>
+      <c r="N103" s="35" t="n"/>
+      <c r="Q103" s="35" t="n"/>
+      <c r="R103" s="35" t="n"/>
+      <c r="S103" s="35" t="n"/>
+      <c r="T103" s="35" t="n"/>
+      <c r="U103" s="35" t="n"/>
+      <c r="V103" s="35" t="n"/>
+      <c r="Y103" s="35" t="n"/>
+      <c r="Z103" s="35" t="n"/>
+      <c r="AA103" s="35" t="n"/>
+      <c r="AB103" s="35" t="n"/>
+      <c r="AC103" s="35" t="n"/>
+      <c r="AD103" s="35" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B106" s="21" t="n"/>
+      <c r="C106" s="21" t="n"/>
+      <c r="D106" s="21" t="n"/>
+      <c r="E106" s="21" t="n"/>
+      <c r="F106" s="22" t="n"/>
+      <c r="I106" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J106" s="21" t="n"/>
+      <c r="K106" s="21" t="n"/>
+      <c r="L106" s="21" t="n"/>
+      <c r="M106" s="21" t="n"/>
+      <c r="N106" s="22" t="n"/>
+      <c r="Q106" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R106" s="21" t="n"/>
+      <c r="S106" s="21" t="n"/>
+      <c r="T106" s="21" t="n"/>
+      <c r="U106" s="21" t="n"/>
+      <c r="V106" s="22" t="n"/>
+      <c r="Y106" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z106" s="21" t="n"/>
+      <c r="AA106" s="21" t="n"/>
+      <c r="AB106" s="21" t="n"/>
+      <c r="AC106" s="21" t="n"/>
+      <c r="AD106" s="22" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" s="23" t="n"/>
+      <c r="B107" s="24" t="n"/>
+      <c r="C107" s="24" t="n"/>
+      <c r="D107" s="24" t="n"/>
+      <c r="E107" s="24" t="n"/>
+      <c r="F107" s="25" t="n"/>
+      <c r="I107" s="23" t="n"/>
+      <c r="J107" s="24" t="n"/>
+      <c r="K107" s="24" t="n"/>
+      <c r="L107" s="24" t="n"/>
+      <c r="M107" s="24" t="n"/>
+      <c r="N107" s="25" t="n"/>
+      <c r="Q107" s="23" t="n"/>
+      <c r="R107" s="24" t="n"/>
+      <c r="S107" s="24" t="n"/>
+      <c r="T107" s="24" t="n"/>
+      <c r="U107" s="24" t="n"/>
+      <c r="V107" s="25" t="n"/>
+      <c r="Y107" s="23" t="n"/>
+      <c r="Z107" s="24" t="n"/>
+      <c r="AA107" s="24" t="n"/>
+      <c r="AB107" s="24" t="n"/>
+      <c r="AC107" s="24" t="n"/>
+      <c r="AD107" s="25" t="n"/>
+    </row>
+    <row r="108">
+      <c r="B108" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C108" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="D108" s="28" t="n">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="J108" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K108" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="L108" s="28" t="n">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="R108" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S108" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="T108" s="28" t="n">
+        <v>0.4861111111111111</v>
+      </c>
+      <c r="Z108" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA108" s="27" t="n">
+        <v>7</v>
+      </c>
+      <c r="AB108" s="28" t="n">
+        <v>0.4861111111111111</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Smart Guy</t>
+        </is>
+      </c>
+      <c r="B109" s="11" t="n"/>
+      <c r="C109" s="11" t="n"/>
+      <c r="D109" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 2</t>
+        </is>
+      </c>
+      <c r="E109" s="11" t="n"/>
+      <c r="F109" s="11" t="n"/>
+      <c r="I109" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Proud Family</t>
+        </is>
+      </c>
+      <c r="J109" s="11" t="n"/>
+      <c r="K109" s="11" t="n"/>
+      <c r="L109" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="M109" s="11" t="n"/>
+      <c r="N109" s="11" t="n"/>
+      <c r="Q109" s="30" t="inlineStr">
+        <is>
+          <t>Ref: That's So Raven</t>
+        </is>
+      </c>
+      <c r="R109" s="11" t="n"/>
+      <c r="S109" s="11" t="n"/>
+      <c r="T109" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="U109" s="11" t="n"/>
+      <c r="V109" s="11" t="n"/>
+      <c r="Y109" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Incredibles</t>
+        </is>
+      </c>
+      <c r="Z109" s="11" t="n"/>
+      <c r="AA109" s="11" t="n"/>
+      <c r="AB109" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="AC109" s="11" t="n"/>
+      <c r="AD109" s="11" t="n"/>
+    </row>
+    <row r="110">
+      <c r="A110" s="31" t="inlineStr">
+        <is>
+          <t>Sister Sister</t>
+        </is>
+      </c>
+      <c r="B110" s="11" t="n"/>
+      <c r="C110" s="11" t="n"/>
+      <c r="D110" s="31" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="E110" s="11" t="n"/>
+      <c r="F110" s="11" t="n"/>
+      <c r="I110" s="31" t="inlineStr">
+        <is>
+          <t>Black Panther</t>
+        </is>
+      </c>
+      <c r="J110" s="11" t="n"/>
+      <c r="K110" s="11" t="n"/>
+      <c r="L110" s="31" t="inlineStr">
+        <is>
+          <t>The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="M110" s="11" t="n"/>
+      <c r="N110" s="11" t="n"/>
+      <c r="Q110" s="31" t="inlineStr">
+        <is>
+          <t>Static Shock</t>
+        </is>
+      </c>
+      <c r="R110" s="11" t="n"/>
+      <c r="S110" s="11" t="n"/>
+      <c r="T110" s="31" t="inlineStr">
+        <is>
+          <t>Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="U110" s="11" t="n"/>
+      <c r="V110" s="11" t="n"/>
+      <c r="Y110" s="31" t="inlineStr">
+        <is>
+          <t>Fillmore</t>
+        </is>
+      </c>
+      <c r="Z110" s="11" t="n"/>
+      <c r="AA110" s="11" t="n"/>
+      <c r="AB110" s="31" t="inlineStr">
+        <is>
+          <t>Abbott Elementary</t>
+        </is>
+      </c>
+      <c r="AC110" s="11" t="n"/>
+      <c r="AD110" s="11" t="n"/>
+    </row>
+    <row r="111">
+      <c r="A111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="n"/>
+      <c r="C111" s="11" t="n"/>
+      <c r="D111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E111" s="11" t="n"/>
+      <c r="F111" s="11" t="n"/>
+      <c r="I111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J111" s="11" t="n"/>
+      <c r="K111" s="11" t="n"/>
+      <c r="L111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M111" s="11" t="n"/>
+      <c r="N111" s="11" t="n"/>
+      <c r="Q111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R111" s="11" t="n"/>
+      <c r="S111" s="11" t="n"/>
+      <c r="T111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U111" s="11" t="n"/>
+      <c r="V111" s="11" t="n"/>
+      <c r="Y111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z111" s="11" t="n"/>
+      <c r="AA111" s="11" t="n"/>
+      <c r="AB111" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC111" s="11" t="n"/>
+      <c r="AD111" s="11" t="n"/>
+    </row>
+    <row r="112">
+      <c r="A112" s="11" t="n"/>
+      <c r="B112" s="11" t="n"/>
+      <c r="C112" s="11" t="n"/>
+      <c r="D112" s="11" t="n"/>
+      <c r="E112" s="11" t="n"/>
+      <c r="F112" s="11" t="n"/>
+      <c r="I112" s="11" t="n"/>
+      <c r="J112" s="11" t="n"/>
+      <c r="K112" s="11" t="n"/>
+      <c r="L112" s="11" t="n"/>
+      <c r="M112" s="11" t="n"/>
+      <c r="N112" s="11" t="n"/>
+      <c r="Q112" s="11" t="n"/>
+      <c r="R112" s="11" t="n"/>
+      <c r="S112" s="11" t="n"/>
+      <c r="T112" s="11" t="n"/>
+      <c r="U112" s="11" t="n"/>
+      <c r="V112" s="11" t="n"/>
+      <c r="Y112" s="11" t="n"/>
+      <c r="Z112" s="11" t="n"/>
+      <c r="AA112" s="11" t="n"/>
+      <c r="AB112" s="11" t="n"/>
+      <c r="AC112" s="11" t="n"/>
+      <c r="AD112" s="11" t="n"/>
+    </row>
+    <row r="113">
+      <c r="A113" s="11" t="n"/>
+      <c r="B113" s="11" t="n"/>
+      <c r="C113" s="11" t="n"/>
+      <c r="D113" s="11" t="n"/>
+      <c r="E113" s="11" t="n"/>
+      <c r="F113" s="11" t="n"/>
+      <c r="I113" s="11" t="n"/>
+      <c r="J113" s="11" t="n"/>
+      <c r="K113" s="11" t="n"/>
+      <c r="L113" s="11" t="n"/>
+      <c r="M113" s="11" t="n"/>
+      <c r="N113" s="11" t="n"/>
+      <c r="Q113" s="11" t="n"/>
+      <c r="R113" s="11" t="n"/>
+      <c r="S113" s="11" t="n"/>
+      <c r="T113" s="11" t="n"/>
+      <c r="U113" s="11" t="n"/>
+      <c r="V113" s="11" t="n"/>
+      <c r="Y113" s="11" t="n"/>
+      <c r="Z113" s="11" t="n"/>
+      <c r="AA113" s="11" t="n"/>
+      <c r="AB113" s="11" t="n"/>
+      <c r="AC113" s="11" t="n"/>
+      <c r="AD113" s="11" t="n"/>
+    </row>
+    <row r="114">
+      <c r="A114" s="11" t="n"/>
+      <c r="B114" s="11" t="n"/>
+      <c r="C114" s="11" t="n"/>
+      <c r="D114" s="11" t="n"/>
+      <c r="E114" s="11" t="n"/>
+      <c r="F114" s="11" t="n"/>
+      <c r="I114" s="11" t="n"/>
+      <c r="J114" s="11" t="n"/>
+      <c r="K114" s="11" t="n"/>
+      <c r="L114" s="11" t="n"/>
+      <c r="M114" s="11" t="n"/>
+      <c r="N114" s="11" t="n"/>
+      <c r="Q114" s="11" t="n"/>
+      <c r="R114" s="11" t="n"/>
+      <c r="S114" s="11" t="n"/>
+      <c r="T114" s="11" t="n"/>
+      <c r="U114" s="11" t="n"/>
+      <c r="V114" s="11" t="n"/>
+      <c r="Y114" s="11" t="n"/>
+      <c r="Z114" s="11" t="n"/>
+      <c r="AA114" s="11" t="n"/>
+      <c r="AB114" s="11" t="n"/>
+      <c r="AC114" s="11" t="n"/>
+      <c r="AD114" s="11" t="n"/>
+    </row>
+    <row r="115">
+      <c r="A115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="B115" s="11" t="n"/>
+      <c r="C115" s="11" t="n"/>
+      <c r="D115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="E115" s="11" t="n"/>
+      <c r="F115" s="11" t="n"/>
+      <c r="I115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 3</t>
+        </is>
+      </c>
+      <c r="J115" s="11" t="n"/>
+      <c r="K115" s="11" t="n"/>
+      <c r="L115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 4</t>
+        </is>
+      </c>
+      <c r="M115" s="11" t="n"/>
+      <c r="N115" s="11" t="n"/>
+      <c r="Q115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R115" s="11" t="n"/>
+      <c r="S115" s="11" t="n"/>
+      <c r="T115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 1</t>
+        </is>
+      </c>
+      <c r="U115" s="11" t="n"/>
+      <c r="V115" s="11" t="n"/>
+      <c r="Y115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="Z115" s="11" t="n"/>
+      <c r="AA115" s="11" t="n"/>
+      <c r="AB115" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 2</t>
+        </is>
+      </c>
+      <c r="AC115" s="11" t="n"/>
+      <c r="AD115" s="11" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="n"/>
+      <c r="C116" s="11" t="n"/>
+      <c r="D116" s="11" t="n"/>
+      <c r="E116" s="11" t="n"/>
+      <c r="F116" s="11" t="n"/>
+      <c r="I116" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J116" s="11" t="n"/>
+      <c r="K116" s="11" t="n"/>
+      <c r="L116" s="11" t="n"/>
+      <c r="M116" s="11" t="n"/>
+      <c r="N116" s="11" t="n"/>
+      <c r="Q116" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R116" s="11" t="n"/>
+      <c r="S116" s="11" t="n"/>
+      <c r="T116" s="11" t="n"/>
+      <c r="U116" s="11" t="n"/>
+      <c r="V116" s="11" t="n"/>
+      <c r="Y116" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z116" s="11" t="n"/>
+      <c r="AA116" s="11" t="n"/>
+      <c r="AB116" s="11" t="n"/>
+      <c r="AC116" s="11" t="n"/>
+      <c r="AD116" s="11" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B117" s="11" t="n"/>
+      <c r="C117" s="11" t="n"/>
+      <c r="D117" s="11" t="n"/>
+      <c r="E117" s="11" t="n"/>
+      <c r="F117" s="11" t="n"/>
+      <c r="I117" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J117" s="11" t="n"/>
+      <c r="K117" s="11" t="n"/>
+      <c r="L117" s="11" t="n"/>
+      <c r="M117" s="11" t="n"/>
+      <c r="N117" s="11" t="n"/>
+      <c r="Q117" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R117" s="11" t="n"/>
+      <c r="S117" s="11" t="n"/>
+      <c r="T117" s="11" t="n"/>
+      <c r="U117" s="11" t="n"/>
+      <c r="V117" s="11" t="n"/>
+      <c r="Y117" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z117" s="11" t="n"/>
+      <c r="AA117" s="11" t="n"/>
+      <c r="AB117" s="11" t="n"/>
+      <c r="AC117" s="11" t="n"/>
+      <c r="AD117" s="11" t="n"/>
+    </row>
+    <row r="118">
+      <c r="A118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="n"/>
+      <c r="C118" s="11" t="n"/>
+      <c r="D118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E118" s="11" t="n"/>
+      <c r="F118" s="11" t="n"/>
+      <c r="I118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J118" s="11" t="n"/>
+      <c r="K118" s="11" t="n"/>
+      <c r="L118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M118" s="11" t="n"/>
+      <c r="N118" s="11" t="n"/>
+      <c r="Q118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R118" s="11" t="n"/>
+      <c r="S118" s="11" t="n"/>
+      <c r="T118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U118" s="11" t="n"/>
+      <c r="V118" s="11" t="n"/>
+      <c r="Y118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z118" s="11" t="n"/>
+      <c r="AA118" s="11" t="n"/>
+      <c r="AB118" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC118" s="11" t="n"/>
+      <c r="AD118" s="11" t="n"/>
+    </row>
+    <row r="119">
+      <c r="A119" s="11" t="n"/>
+      <c r="B119" s="11" t="n"/>
+      <c r="C119" s="11" t="n"/>
+      <c r="D119" s="11" t="n"/>
+      <c r="E119" s="11" t="n"/>
+      <c r="F119" s="11" t="n"/>
+      <c r="I119" s="11" t="n"/>
+      <c r="J119" s="11" t="n"/>
+      <c r="K119" s="11" t="n"/>
+      <c r="L119" s="11" t="n"/>
+      <c r="M119" s="11" t="n"/>
+      <c r="N119" s="11" t="n"/>
+      <c r="Q119" s="11" t="n"/>
+      <c r="R119" s="11" t="n"/>
+      <c r="S119" s="11" t="n"/>
+      <c r="T119" s="11" t="n"/>
+      <c r="U119" s="11" t="n"/>
+      <c r="V119" s="11" t="n"/>
+      <c r="Y119" s="11" t="n"/>
+      <c r="Z119" s="11" t="n"/>
+      <c r="AA119" s="11" t="n"/>
+      <c r="AB119" s="11" t="n"/>
+      <c r="AC119" s="11" t="n"/>
+      <c r="AD119" s="11" t="n"/>
+    </row>
+    <row r="120">
+      <c r="A120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B120" s="35" t="n"/>
+      <c r="C120" s="35" t="n"/>
+      <c r="D120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E120" s="35" t="n"/>
+      <c r="F120" s="35" t="n"/>
+      <c r="I120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J120" s="35" t="n"/>
+      <c r="K120" s="35" t="n"/>
+      <c r="L120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M120" s="35" t="n"/>
+      <c r="N120" s="35" t="n"/>
+      <c r="Q120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R120" s="35" t="n"/>
+      <c r="S120" s="35" t="n"/>
+      <c r="T120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U120" s="35" t="n"/>
+      <c r="V120" s="35" t="n"/>
+      <c r="Y120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z120" s="35" t="n"/>
+      <c r="AA120" s="35" t="n"/>
+      <c r="AB120" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC120" s="35" t="n"/>
+      <c r="AD120" s="35" t="n"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="35" t="n"/>
+      <c r="B121" s="35" t="n"/>
+      <c r="C121" s="35" t="n"/>
+      <c r="D121" s="35" t="n"/>
+      <c r="E121" s="35" t="n"/>
+      <c r="F121" s="35" t="n"/>
+      <c r="I121" s="35" t="n"/>
+      <c r="J121" s="35" t="n"/>
+      <c r="K121" s="35" t="n"/>
+      <c r="L121" s="35" t="n"/>
+      <c r="M121" s="35" t="n"/>
+      <c r="N121" s="35" t="n"/>
+      <c r="Q121" s="35" t="n"/>
+      <c r="R121" s="35" t="n"/>
+      <c r="S121" s="35" t="n"/>
+      <c r="T121" s="35" t="n"/>
+      <c r="U121" s="35" t="n"/>
+      <c r="V121" s="35" t="n"/>
+      <c r="Y121" s="35" t="n"/>
+      <c r="Z121" s="35" t="n"/>
+      <c r="AA121" s="35" t="n"/>
+      <c r="AB121" s="35" t="n"/>
+      <c r="AC121" s="35" t="n"/>
+      <c r="AD121" s="35" t="n"/>
+    </row>
+    <row r="123">
+      <c r="A123" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B123" s="21" t="n"/>
+      <c r="C123" s="21" t="n"/>
+      <c r="D123" s="21" t="n"/>
+      <c r="E123" s="21" t="n"/>
+      <c r="F123" s="22" t="n"/>
+      <c r="I123" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J123" s="21" t="n"/>
+      <c r="K123" s="21" t="n"/>
+      <c r="L123" s="21" t="n"/>
+      <c r="M123" s="21" t="n"/>
+      <c r="N123" s="22" t="n"/>
+      <c r="Q123" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R123" s="21" t="n"/>
+      <c r="S123" s="21" t="n"/>
+      <c r="T123" s="21" t="n"/>
+      <c r="U123" s="21" t="n"/>
+      <c r="V123" s="22" t="n"/>
+      <c r="Y123" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z123" s="21" t="n"/>
+      <c r="AA123" s="21" t="n"/>
+      <c r="AB123" s="21" t="n"/>
+      <c r="AC123" s="21" t="n"/>
+      <c r="AD123" s="22" t="n"/>
+    </row>
+    <row r="124">
+      <c r="A124" s="23" t="n"/>
+      <c r="B124" s="24" t="n"/>
+      <c r="C124" s="24" t="n"/>
+      <c r="D124" s="24" t="n"/>
+      <c r="E124" s="24" t="n"/>
+      <c r="F124" s="25" t="n"/>
+      <c r="I124" s="23" t="n"/>
+      <c r="J124" s="24" t="n"/>
+      <c r="K124" s="24" t="n"/>
+      <c r="L124" s="24" t="n"/>
+      <c r="M124" s="24" t="n"/>
+      <c r="N124" s="25" t="n"/>
+      <c r="Q124" s="23" t="n"/>
+      <c r="R124" s="24" t="n"/>
+      <c r="S124" s="24" t="n"/>
+      <c r="T124" s="24" t="n"/>
+      <c r="U124" s="24" t="n"/>
+      <c r="V124" s="25" t="n"/>
+      <c r="Y124" s="23" t="n"/>
+      <c r="Z124" s="24" t="n"/>
+      <c r="AA124" s="24" t="n"/>
+      <c r="AB124" s="24" t="n"/>
+      <c r="AC124" s="24" t="n"/>
+      <c r="AD124" s="25" t="n"/>
+    </row>
+    <row r="125">
+      <c r="B125" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C125" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="D125" s="28" t="n">
+        <v>0.5034722222222222</v>
+      </c>
+      <c r="J125" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K125" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="L125" s="28" t="n">
+        <v>0.5034722222222222</v>
+      </c>
+      <c r="R125" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S125" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="T125" s="28" t="n">
+        <v>0.5034722222222222</v>
+      </c>
+      <c r="Z125" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA125" s="27" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB125" s="28" t="n">
+        <v>0.5034722222222222</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="n"/>
+      <c r="C126" s="11" t="n"/>
+      <c r="D126" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="E126" s="11" t="n"/>
+      <c r="F126" s="11" t="n"/>
+      <c r="I126" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Abbott Elementary</t>
+        </is>
+      </c>
+      <c r="J126" s="11" t="n"/>
+      <c r="K126" s="11" t="n"/>
+      <c r="L126" s="30" t="inlineStr">
+        <is>
+          <t>Next: OFF</t>
+        </is>
+      </c>
+      <c r="M126" s="11" t="n"/>
+      <c r="N126" s="11" t="n"/>
+      <c r="Q126" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Black Panther</t>
+        </is>
+      </c>
+      <c r="R126" s="11" t="n"/>
+      <c r="S126" s="11" t="n"/>
+      <c r="T126" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 2</t>
+        </is>
+      </c>
+      <c r="U126" s="11" t="n"/>
+      <c r="V126" s="11" t="n"/>
+      <c r="Y126" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="Z126" s="11" t="n"/>
+      <c r="AA126" s="11" t="n"/>
+      <c r="AB126" s="30" t="inlineStr">
+        <is>
+          <t>Next: Ref Court 2</t>
+        </is>
+      </c>
+      <c r="AC126" s="11" t="n"/>
+      <c r="AD126" s="11" t="n"/>
+    </row>
+    <row r="127">
+      <c r="A127" s="31" t="inlineStr">
+        <is>
+          <t>Family Matters</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="n"/>
+      <c r="C127" s="11" t="n"/>
+      <c r="D127" s="31" t="inlineStr">
+        <is>
+          <t>The Boondocks</t>
+        </is>
+      </c>
+      <c r="E127" s="11" t="n"/>
+      <c r="F127" s="11" t="n"/>
+      <c r="I127" s="31" t="inlineStr">
+        <is>
+          <t>Fresh Prince</t>
+        </is>
+      </c>
+      <c r="J127" s="11" t="n"/>
+      <c r="K127" s="11" t="n"/>
+      <c r="L127" s="31" t="inlineStr">
+        <is>
+          <t>Smart Guy</t>
+        </is>
+      </c>
+      <c r="M127" s="11" t="n"/>
+      <c r="N127" s="11" t="n"/>
+      <c r="Q127" s="31" t="inlineStr">
+        <is>
+          <t>The Incredibles</t>
+        </is>
+      </c>
+      <c r="R127" s="11" t="n"/>
+      <c r="S127" s="11" t="n"/>
+      <c r="T127" s="31" t="inlineStr">
+        <is>
+          <t>That's So Raven</t>
+        </is>
+      </c>
+      <c r="U127" s="11" t="n"/>
+      <c r="V127" s="11" t="n"/>
+      <c r="Y127" s="31" t="inlineStr">
+        <is>
+          <t>Proud Family</t>
+        </is>
+      </c>
+      <c r="Z127" s="11" t="n"/>
+      <c r="AA127" s="11" t="n"/>
+      <c r="AB127" s="31" t="inlineStr">
+        <is>
+          <t>The Parkers</t>
+        </is>
+      </c>
+      <c r="AC127" s="11" t="n"/>
+      <c r="AD127" s="11" t="n"/>
+    </row>
+    <row r="128">
+      <c r="A128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="n"/>
+      <c r="C128" s="11" t="n"/>
+      <c r="D128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E128" s="11" t="n"/>
+      <c r="F128" s="11" t="n"/>
+      <c r="I128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J128" s="11" t="n"/>
+      <c r="K128" s="11" t="n"/>
+      <c r="L128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M128" s="11" t="n"/>
+      <c r="N128" s="11" t="n"/>
+      <c r="Q128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R128" s="11" t="n"/>
+      <c r="S128" s="11" t="n"/>
+      <c r="T128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U128" s="11" t="n"/>
+      <c r="V128" s="11" t="n"/>
+      <c r="Y128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z128" s="11" t="n"/>
+      <c r="AA128" s="11" t="n"/>
+      <c r="AB128" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC128" s="11" t="n"/>
+      <c r="AD128" s="11" t="n"/>
+    </row>
+    <row r="129">
+      <c r="A129" s="11" t="n"/>
+      <c r="B129" s="11" t="n"/>
+      <c r="C129" s="11" t="n"/>
+      <c r="D129" s="11" t="n"/>
+      <c r="E129" s="11" t="n"/>
+      <c r="F129" s="11" t="n"/>
+      <c r="I129" s="11" t="n"/>
+      <c r="J129" s="11" t="n"/>
+      <c r="K129" s="11" t="n"/>
+      <c r="L129" s="11" t="n"/>
+      <c r="M129" s="11" t="n"/>
+      <c r="N129" s="11" t="n"/>
+      <c r="Q129" s="11" t="n"/>
+      <c r="R129" s="11" t="n"/>
+      <c r="S129" s="11" t="n"/>
+      <c r="T129" s="11" t="n"/>
+      <c r="U129" s="11" t="n"/>
+      <c r="V129" s="11" t="n"/>
+      <c r="Y129" s="11" t="n"/>
+      <c r="Z129" s="11" t="n"/>
+      <c r="AA129" s="11" t="n"/>
+      <c r="AB129" s="11" t="n"/>
+      <c r="AC129" s="11" t="n"/>
+      <c r="AD129" s="11" t="n"/>
+    </row>
+    <row r="130">
+      <c r="A130" s="11" t="n"/>
+      <c r="B130" s="11" t="n"/>
+      <c r="C130" s="11" t="n"/>
+      <c r="D130" s="11" t="n"/>
+      <c r="E130" s="11" t="n"/>
+      <c r="F130" s="11" t="n"/>
+      <c r="I130" s="11" t="n"/>
+      <c r="J130" s="11" t="n"/>
+      <c r="K130" s="11" t="n"/>
+      <c r="L130" s="11" t="n"/>
+      <c r="M130" s="11" t="n"/>
+      <c r="N130" s="11" t="n"/>
+      <c r="Q130" s="11" t="n"/>
+      <c r="R130" s="11" t="n"/>
+      <c r="S130" s="11" t="n"/>
+      <c r="T130" s="11" t="n"/>
+      <c r="U130" s="11" t="n"/>
+      <c r="V130" s="11" t="n"/>
+      <c r="Y130" s="11" t="n"/>
+      <c r="Z130" s="11" t="n"/>
+      <c r="AA130" s="11" t="n"/>
+      <c r="AB130" s="11" t="n"/>
+      <c r="AC130" s="11" t="n"/>
+      <c r="AD130" s="11" t="n"/>
+    </row>
+    <row r="131">
+      <c r="A131" s="11" t="n"/>
+      <c r="B131" s="11" t="n"/>
+      <c r="C131" s="11" t="n"/>
+      <c r="D131" s="11" t="n"/>
+      <c r="E131" s="11" t="n"/>
+      <c r="F131" s="11" t="n"/>
+      <c r="I131" s="11" t="n"/>
+      <c r="J131" s="11" t="n"/>
+      <c r="K131" s="11" t="n"/>
+      <c r="L131" s="11" t="n"/>
+      <c r="M131" s="11" t="n"/>
+      <c r="N131" s="11" t="n"/>
+      <c r="Q131" s="11" t="n"/>
+      <c r="R131" s="11" t="n"/>
+      <c r="S131" s="11" t="n"/>
+      <c r="T131" s="11" t="n"/>
+      <c r="U131" s="11" t="n"/>
+      <c r="V131" s="11" t="n"/>
+      <c r="Y131" s="11" t="n"/>
+      <c r="Z131" s="11" t="n"/>
+      <c r="AA131" s="11" t="n"/>
+      <c r="AB131" s="11" t="n"/>
+      <c r="AC131" s="11" t="n"/>
+      <c r="AD131" s="11" t="n"/>
+    </row>
+    <row r="132">
+      <c r="A132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Court 3</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="n"/>
+      <c r="C132" s="11" t="n"/>
+      <c r="D132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 1</t>
+        </is>
+      </c>
+      <c r="E132" s="11" t="n"/>
+      <c r="F132" s="11" t="n"/>
+      <c r="I132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 3</t>
+        </is>
+      </c>
+      <c r="J132" s="11" t="n"/>
+      <c r="K132" s="11" t="n"/>
+      <c r="L132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 3</t>
+        </is>
+      </c>
+      <c r="M132" s="11" t="n"/>
+      <c r="N132" s="11" t="n"/>
+      <c r="Q132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R132" s="11" t="n"/>
+      <c r="S132" s="11" t="n"/>
+      <c r="T132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="U132" s="11" t="n"/>
+      <c r="V132" s="11" t="n"/>
+      <c r="Y132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="Z132" s="11" t="n"/>
+      <c r="AA132" s="11" t="n"/>
+      <c r="AB132" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Court 2</t>
+        </is>
+      </c>
+      <c r="AC132" s="11" t="n"/>
+      <c r="AD132" s="11" t="n"/>
+    </row>
+    <row r="133">
+      <c r="A133" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B133" s="11" t="n"/>
+      <c r="C133" s="11" t="n"/>
+      <c r="D133" s="11" t="n"/>
+      <c r="E133" s="11" t="n"/>
+      <c r="F133" s="11" t="n"/>
+      <c r="I133" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J133" s="11" t="n"/>
+      <c r="K133" s="11" t="n"/>
+      <c r="L133" s="11" t="n"/>
+      <c r="M133" s="11" t="n"/>
+      <c r="N133" s="11" t="n"/>
+      <c r="Q133" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R133" s="11" t="n"/>
+      <c r="S133" s="11" t="n"/>
+      <c r="T133" s="11" t="n"/>
+      <c r="U133" s="11" t="n"/>
+      <c r="V133" s="11" t="n"/>
+      <c r="Y133" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z133" s="11" t="n"/>
+      <c r="AA133" s="11" t="n"/>
+      <c r="AB133" s="11" t="n"/>
+      <c r="AC133" s="11" t="n"/>
+      <c r="AD133" s="11" t="n"/>
+    </row>
+    <row r="134">
+      <c r="A134" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B134" s="11" t="n"/>
+      <c r="C134" s="11" t="n"/>
+      <c r="D134" s="11" t="n"/>
+      <c r="E134" s="11" t="n"/>
+      <c r="F134" s="11" t="n"/>
+      <c r="I134" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J134" s="11" t="n"/>
+      <c r="K134" s="11" t="n"/>
+      <c r="L134" s="11" t="n"/>
+      <c r="M134" s="11" t="n"/>
+      <c r="N134" s="11" t="n"/>
+      <c r="Q134" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R134" s="11" t="n"/>
+      <c r="S134" s="11" t="n"/>
+      <c r="T134" s="11" t="n"/>
+      <c r="U134" s="11" t="n"/>
+      <c r="V134" s="11" t="n"/>
+      <c r="Y134" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z134" s="11" t="n"/>
+      <c r="AA134" s="11" t="n"/>
+      <c r="AB134" s="11" t="n"/>
+      <c r="AC134" s="11" t="n"/>
+      <c r="AD134" s="11" t="n"/>
+    </row>
+    <row r="135">
+      <c r="A135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B135" s="11" t="n"/>
+      <c r="C135" s="11" t="n"/>
+      <c r="D135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E135" s="11" t="n"/>
+      <c r="F135" s="11" t="n"/>
+      <c r="I135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J135" s="11" t="n"/>
+      <c r="K135" s="11" t="n"/>
+      <c r="L135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M135" s="11" t="n"/>
+      <c r="N135" s="11" t="n"/>
+      <c r="Q135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R135" s="11" t="n"/>
+      <c r="S135" s="11" t="n"/>
+      <c r="T135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U135" s="11" t="n"/>
+      <c r="V135" s="11" t="n"/>
+      <c r="Y135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z135" s="11" t="n"/>
+      <c r="AA135" s="11" t="n"/>
+      <c r="AB135" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC135" s="11" t="n"/>
+      <c r="AD135" s="11" t="n"/>
+    </row>
+    <row r="136">
+      <c r="A136" s="11" t="n"/>
+      <c r="B136" s="11" t="n"/>
+      <c r="C136" s="11" t="n"/>
+      <c r="D136" s="11" t="n"/>
+      <c r="E136" s="11" t="n"/>
+      <c r="F136" s="11" t="n"/>
+      <c r="I136" s="11" t="n"/>
+      <c r="J136" s="11" t="n"/>
+      <c r="K136" s="11" t="n"/>
+      <c r="L136" s="11" t="n"/>
+      <c r="M136" s="11" t="n"/>
+      <c r="N136" s="11" t="n"/>
+      <c r="Q136" s="11" t="n"/>
+      <c r="R136" s="11" t="n"/>
+      <c r="S136" s="11" t="n"/>
+      <c r="T136" s="11" t="n"/>
+      <c r="U136" s="11" t="n"/>
+      <c r="V136" s="11" t="n"/>
+      <c r="Y136" s="11" t="n"/>
+      <c r="Z136" s="11" t="n"/>
+      <c r="AA136" s="11" t="n"/>
+      <c r="AB136" s="11" t="n"/>
+      <c r="AC136" s="11" t="n"/>
+      <c r="AD136" s="11" t="n"/>
+    </row>
+    <row r="137">
+      <c r="A137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B137" s="35" t="n"/>
+      <c r="C137" s="35" t="n"/>
+      <c r="D137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E137" s="35" t="n"/>
+      <c r="F137" s="35" t="n"/>
+      <c r="I137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J137" s="35" t="n"/>
+      <c r="K137" s="35" t="n"/>
+      <c r="L137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M137" s="35" t="n"/>
+      <c r="N137" s="35" t="n"/>
+      <c r="Q137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R137" s="35" t="n"/>
+      <c r="S137" s="35" t="n"/>
+      <c r="T137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U137" s="35" t="n"/>
+      <c r="V137" s="35" t="n"/>
+      <c r="Y137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z137" s="35" t="n"/>
+      <c r="AA137" s="35" t="n"/>
+      <c r="AB137" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC137" s="35" t="n"/>
+      <c r="AD137" s="35" t="n"/>
+    </row>
+    <row r="138">
+      <c r="A138" s="35" t="n"/>
+      <c r="B138" s="35" t="n"/>
+      <c r="C138" s="35" t="n"/>
+      <c r="D138" s="35" t="n"/>
+      <c r="E138" s="35" t="n"/>
+      <c r="F138" s="35" t="n"/>
+      <c r="I138" s="35" t="n"/>
+      <c r="J138" s="35" t="n"/>
+      <c r="K138" s="35" t="n"/>
+      <c r="L138" s="35" t="n"/>
+      <c r="M138" s="35" t="n"/>
+      <c r="N138" s="35" t="n"/>
+      <c r="Q138" s="35" t="n"/>
+      <c r="R138" s="35" t="n"/>
+      <c r="S138" s="35" t="n"/>
+      <c r="T138" s="35" t="n"/>
+      <c r="U138" s="35" t="n"/>
+      <c r="V138" s="35" t="n"/>
+      <c r="Y138" s="35" t="n"/>
+      <c r="Z138" s="35" t="n"/>
+      <c r="AA138" s="35" t="n"/>
+      <c r="AB138" s="35" t="n"/>
+      <c r="AC138" s="35" t="n"/>
+      <c r="AD138" s="35" t="n"/>
+    </row>
+    <row r="141">
+      <c r="A141" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B141" s="21" t="n"/>
+      <c r="C141" s="21" t="n"/>
+      <c r="D141" s="21" t="n"/>
+      <c r="E141" s="21" t="n"/>
+      <c r="F141" s="22" t="n"/>
+      <c r="I141" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J141" s="21" t="n"/>
+      <c r="K141" s="21" t="n"/>
+      <c r="L141" s="21" t="n"/>
+      <c r="M141" s="21" t="n"/>
+      <c r="N141" s="22" t="n"/>
+      <c r="Q141" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R141" s="21" t="n"/>
+      <c r="S141" s="21" t="n"/>
+      <c r="T141" s="21" t="n"/>
+      <c r="U141" s="21" t="n"/>
+      <c r="V141" s="22" t="n"/>
+      <c r="Y141" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z141" s="21" t="n"/>
+      <c r="AA141" s="21" t="n"/>
+      <c r="AB141" s="21" t="n"/>
+      <c r="AC141" s="21" t="n"/>
+      <c r="AD141" s="22" t="n"/>
+    </row>
+    <row r="142">
+      <c r="A142" s="23" t="n"/>
+      <c r="B142" s="24" t="n"/>
+      <c r="C142" s="24" t="n"/>
+      <c r="D142" s="24" t="n"/>
+      <c r="E142" s="24" t="n"/>
+      <c r="F142" s="25" t="n"/>
+      <c r="I142" s="23" t="n"/>
+      <c r="J142" s="24" t="n"/>
+      <c r="K142" s="24" t="n"/>
+      <c r="L142" s="24" t="n"/>
+      <c r="M142" s="24" t="n"/>
+      <c r="N142" s="25" t="n"/>
+      <c r="Q142" s="23" t="n"/>
+      <c r="R142" s="24" t="n"/>
+      <c r="S142" s="24" t="n"/>
+      <c r="T142" s="24" t="n"/>
+      <c r="U142" s="24" t="n"/>
+      <c r="V142" s="25" t="n"/>
+      <c r="Y142" s="23" t="n"/>
+      <c r="Z142" s="24" t="n"/>
+      <c r="AA142" s="24" t="n"/>
+      <c r="AB142" s="24" t="n"/>
+      <c r="AC142" s="24" t="n"/>
+      <c r="AD142" s="25" t="n"/>
+    </row>
+    <row r="143">
+      <c r="B143" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C143" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D143" s="28" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="J143" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K143" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="L143" s="28" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="R143" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S143" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="T143" s="28" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="Z143" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA143" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB143" s="28" t="n">
+        <v>0.5208333333333334</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Boondocks</t>
+        </is>
+      </c>
+      <c r="B144" s="11" t="n"/>
+      <c r="C144" s="11" t="n"/>
+      <c r="D144" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="E144" s="11" t="n"/>
+      <c r="F144" s="11" t="n"/>
+      <c r="I144" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="J144" s="11" t="n"/>
+      <c r="K144" s="11" t="n"/>
+      <c r="L144" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 4</t>
+        </is>
+      </c>
+      <c r="M144" s="11" t="n"/>
+      <c r="N144" s="11" t="n"/>
+      <c r="Q144" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Fresh Prince</t>
+        </is>
+      </c>
+      <c r="R144" s="11" t="n"/>
+      <c r="S144" s="11" t="n"/>
+      <c r="T144" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 3</t>
+        </is>
+      </c>
+      <c r="U144" s="11" t="n"/>
+      <c r="V144" s="11" t="n"/>
+      <c r="Y144" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Fillmore</t>
+        </is>
+      </c>
+      <c r="Z144" s="11" t="n"/>
+      <c r="AA144" s="11" t="n"/>
+      <c r="AB144" s="30" t="inlineStr">
+        <is>
+          <t>Next: Court 1</t>
+        </is>
+      </c>
+      <c r="AC144" s="11" t="n"/>
+      <c r="AD144" s="11" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="31" t="inlineStr">
+        <is>
+          <t>Static Shock</t>
+        </is>
+      </c>
+      <c r="B145" s="11" t="n"/>
+      <c r="C145" s="11" t="n"/>
+      <c r="D145" s="31" t="inlineStr">
+        <is>
+          <t>Martin</t>
+        </is>
+      </c>
+      <c r="E145" s="11" t="n"/>
+      <c r="F145" s="11" t="n"/>
+      <c r="I145" s="31" t="inlineStr">
+        <is>
+          <t>Black Panther</t>
+        </is>
+      </c>
+      <c r="J145" s="11" t="n"/>
+      <c r="K145" s="11" t="n"/>
+      <c r="L145" s="31" t="inlineStr">
+        <is>
+          <t>The Parkers</t>
+        </is>
+      </c>
+      <c r="M145" s="11" t="n"/>
+      <c r="N145" s="11" t="n"/>
+      <c r="Q145" s="31" t="inlineStr">
+        <is>
+          <t>Family Matters</t>
+        </is>
+      </c>
+      <c r="R145" s="11" t="n"/>
+      <c r="S145" s="11" t="n"/>
+      <c r="T145" s="31" t="inlineStr">
+        <is>
+          <t>Smart Guy</t>
+        </is>
+      </c>
+      <c r="U145" s="11" t="n"/>
+      <c r="V145" s="11" t="n"/>
+      <c r="Y145" s="31" t="inlineStr">
+        <is>
+          <t>Sister Sister</t>
+        </is>
+      </c>
+      <c r="Z145" s="11" t="n"/>
+      <c r="AA145" s="11" t="n"/>
+      <c r="AB145" s="31" t="inlineStr">
+        <is>
+          <t>Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="AC145" s="11" t="n"/>
+      <c r="AD145" s="11" t="n"/>
+    </row>
+    <row r="146">
+      <c r="A146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="n"/>
+      <c r="C146" s="11" t="n"/>
+      <c r="D146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E146" s="11" t="n"/>
+      <c r="F146" s="11" t="n"/>
+      <c r="I146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J146" s="11" t="n"/>
+      <c r="K146" s="11" t="n"/>
+      <c r="L146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M146" s="11" t="n"/>
+      <c r="N146" s="11" t="n"/>
+      <c r="Q146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R146" s="11" t="n"/>
+      <c r="S146" s="11" t="n"/>
+      <c r="T146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U146" s="11" t="n"/>
+      <c r="V146" s="11" t="n"/>
+      <c r="Y146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z146" s="11" t="n"/>
+      <c r="AA146" s="11" t="n"/>
+      <c r="AB146" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC146" s="11" t="n"/>
+      <c r="AD146" s="11" t="n"/>
+    </row>
+    <row r="147">
+      <c r="A147" s="11" t="n"/>
+      <c r="B147" s="11" t="n"/>
+      <c r="C147" s="11" t="n"/>
+      <c r="D147" s="11" t="n"/>
+      <c r="E147" s="11" t="n"/>
+      <c r="F147" s="11" t="n"/>
+      <c r="I147" s="11" t="n"/>
+      <c r="J147" s="11" t="n"/>
+      <c r="K147" s="11" t="n"/>
+      <c r="L147" s="11" t="n"/>
+      <c r="M147" s="11" t="n"/>
+      <c r="N147" s="11" t="n"/>
+      <c r="Q147" s="11" t="n"/>
+      <c r="R147" s="11" t="n"/>
+      <c r="S147" s="11" t="n"/>
+      <c r="T147" s="11" t="n"/>
+      <c r="U147" s="11" t="n"/>
+      <c r="V147" s="11" t="n"/>
+      <c r="Y147" s="11" t="n"/>
+      <c r="Z147" s="11" t="n"/>
+      <c r="AA147" s="11" t="n"/>
+      <c r="AB147" s="11" t="n"/>
+      <c r="AC147" s="11" t="n"/>
+      <c r="AD147" s="11" t="n"/>
+    </row>
+    <row r="148">
+      <c r="A148" s="11" t="n"/>
+      <c r="B148" s="11" t="n"/>
+      <c r="C148" s="11" t="n"/>
+      <c r="D148" s="11" t="n"/>
+      <c r="E148" s="11" t="n"/>
+      <c r="F148" s="11" t="n"/>
+      <c r="I148" s="11" t="n"/>
+      <c r="J148" s="11" t="n"/>
+      <c r="K148" s="11" t="n"/>
+      <c r="L148" s="11" t="n"/>
+      <c r="M148" s="11" t="n"/>
+      <c r="N148" s="11" t="n"/>
+      <c r="Q148" s="11" t="n"/>
+      <c r="R148" s="11" t="n"/>
+      <c r="S148" s="11" t="n"/>
+      <c r="T148" s="11" t="n"/>
+      <c r="U148" s="11" t="n"/>
+      <c r="V148" s="11" t="n"/>
+      <c r="Y148" s="11" t="n"/>
+      <c r="Z148" s="11" t="n"/>
+      <c r="AA148" s="11" t="n"/>
+      <c r="AB148" s="11" t="n"/>
+      <c r="AC148" s="11" t="n"/>
+      <c r="AD148" s="11" t="n"/>
+    </row>
+    <row r="149">
+      <c r="A149" s="11" t="n"/>
+      <c r="B149" s="11" t="n"/>
+      <c r="C149" s="11" t="n"/>
+      <c r="D149" s="11" t="n"/>
+      <c r="E149" s="11" t="n"/>
+      <c r="F149" s="11" t="n"/>
+      <c r="I149" s="11" t="n"/>
+      <c r="J149" s="11" t="n"/>
+      <c r="K149" s="11" t="n"/>
+      <c r="L149" s="11" t="n"/>
+      <c r="M149" s="11" t="n"/>
+      <c r="N149" s="11" t="n"/>
+      <c r="Q149" s="11" t="n"/>
+      <c r="R149" s="11" t="n"/>
+      <c r="S149" s="11" t="n"/>
+      <c r="T149" s="11" t="n"/>
+      <c r="U149" s="11" t="n"/>
+      <c r="V149" s="11" t="n"/>
+      <c r="Y149" s="11" t="n"/>
+      <c r="Z149" s="11" t="n"/>
+      <c r="AA149" s="11" t="n"/>
+      <c r="AB149" s="11" t="n"/>
+      <c r="AC149" s="11" t="n"/>
+      <c r="AD149" s="11" t="n"/>
+    </row>
+    <row r="150">
+      <c r="A150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="B150" s="11" t="n"/>
+      <c r="C150" s="11" t="n"/>
+      <c r="D150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 4</t>
+        </is>
+      </c>
+      <c r="E150" s="11" t="n"/>
+      <c r="F150" s="11" t="n"/>
+      <c r="I150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="J150" s="11" t="n"/>
+      <c r="K150" s="11" t="n"/>
+      <c r="L150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 3</t>
+        </is>
+      </c>
+      <c r="M150" s="11" t="n"/>
+      <c r="N150" s="11" t="n"/>
+      <c r="Q150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  OFF</t>
+        </is>
+      </c>
+      <c r="R150" s="11" t="n"/>
+      <c r="S150" s="11" t="n"/>
+      <c r="T150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: OFF</t>
+        </is>
+      </c>
+      <c r="U150" s="11" t="n"/>
+      <c r="V150" s="11" t="n"/>
+      <c r="Y150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Ref Court 1</t>
+        </is>
+      </c>
+      <c r="Z150" s="11" t="n"/>
+      <c r="AA150" s="11" t="n"/>
+      <c r="AB150" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Ref Court 2</t>
+        </is>
+      </c>
+      <c r="AC150" s="11" t="n"/>
+      <c r="AD150" s="11" t="n"/>
+    </row>
+    <row r="151">
+      <c r="A151" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B151" s="11" t="n"/>
+      <c r="C151" s="11" t="n"/>
+      <c r="D151" s="11" t="n"/>
+      <c r="E151" s="11" t="n"/>
+      <c r="F151" s="11" t="n"/>
+      <c r="I151" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J151" s="11" t="n"/>
+      <c r="K151" s="11" t="n"/>
+      <c r="L151" s="11" t="n"/>
+      <c r="M151" s="11" t="n"/>
+      <c r="N151" s="11" t="n"/>
+      <c r="Q151" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R151" s="11" t="n"/>
+      <c r="S151" s="11" t="n"/>
+      <c r="T151" s="11" t="n"/>
+      <c r="U151" s="11" t="n"/>
+      <c r="V151" s="11" t="n"/>
+      <c r="Y151" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z151" s="11" t="n"/>
+      <c r="AA151" s="11" t="n"/>
+      <c r="AB151" s="11" t="n"/>
+      <c r="AC151" s="11" t="n"/>
+      <c r="AD151" s="11" t="n"/>
+    </row>
+    <row r="152">
+      <c r="A152" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B152" s="11" t="n"/>
+      <c r="C152" s="11" t="n"/>
+      <c r="D152" s="11" t="n"/>
+      <c r="E152" s="11" t="n"/>
+      <c r="F152" s="11" t="n"/>
+      <c r="I152" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J152" s="11" t="n"/>
+      <c r="K152" s="11" t="n"/>
+      <c r="L152" s="11" t="n"/>
+      <c r="M152" s="11" t="n"/>
+      <c r="N152" s="11" t="n"/>
+      <c r="Q152" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R152" s="11" t="n"/>
+      <c r="S152" s="11" t="n"/>
+      <c r="T152" s="11" t="n"/>
+      <c r="U152" s="11" t="n"/>
+      <c r="V152" s="11" t="n"/>
+      <c r="Y152" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z152" s="11" t="n"/>
+      <c r="AA152" s="11" t="n"/>
+      <c r="AB152" s="11" t="n"/>
+      <c r="AC152" s="11" t="n"/>
+      <c r="AD152" s="11" t="n"/>
+    </row>
+    <row r="153">
+      <c r="A153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B153" s="11" t="n"/>
+      <c r="C153" s="11" t="n"/>
+      <c r="D153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E153" s="11" t="n"/>
+      <c r="F153" s="11" t="n"/>
+      <c r="I153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J153" s="11" t="n"/>
+      <c r="K153" s="11" t="n"/>
+      <c r="L153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M153" s="11" t="n"/>
+      <c r="N153" s="11" t="n"/>
+      <c r="Q153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R153" s="11" t="n"/>
+      <c r="S153" s="11" t="n"/>
+      <c r="T153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U153" s="11" t="n"/>
+      <c r="V153" s="11" t="n"/>
+      <c r="Y153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z153" s="11" t="n"/>
+      <c r="AA153" s="11" t="n"/>
+      <c r="AB153" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC153" s="11" t="n"/>
+      <c r="AD153" s="11" t="n"/>
+    </row>
+    <row r="154">
+      <c r="A154" s="11" t="n"/>
+      <c r="B154" s="11" t="n"/>
+      <c r="C154" s="11" t="n"/>
+      <c r="D154" s="11" t="n"/>
+      <c r="E154" s="11" t="n"/>
+      <c r="F154" s="11" t="n"/>
+      <c r="I154" s="11" t="n"/>
+      <c r="J154" s="11" t="n"/>
+      <c r="K154" s="11" t="n"/>
+      <c r="L154" s="11" t="n"/>
+      <c r="M154" s="11" t="n"/>
+      <c r="N154" s="11" t="n"/>
+      <c r="Q154" s="11" t="n"/>
+      <c r="R154" s="11" t="n"/>
+      <c r="S154" s="11" t="n"/>
+      <c r="T154" s="11" t="n"/>
+      <c r="U154" s="11" t="n"/>
+      <c r="V154" s="11" t="n"/>
+      <c r="Y154" s="11" t="n"/>
+      <c r="Z154" s="11" t="n"/>
+      <c r="AA154" s="11" t="n"/>
+      <c r="AB154" s="11" t="n"/>
+      <c r="AC154" s="11" t="n"/>
+      <c r="AD154" s="11" t="n"/>
+    </row>
+    <row r="155">
+      <c r="A155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B155" s="35" t="n"/>
+      <c r="C155" s="35" t="n"/>
+      <c r="D155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E155" s="35" t="n"/>
+      <c r="F155" s="35" t="n"/>
+      <c r="I155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J155" s="35" t="n"/>
+      <c r="K155" s="35" t="n"/>
+      <c r="L155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M155" s="35" t="n"/>
+      <c r="N155" s="35" t="n"/>
+      <c r="Q155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R155" s="35" t="n"/>
+      <c r="S155" s="35" t="n"/>
+      <c r="T155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U155" s="35" t="n"/>
+      <c r="V155" s="35" t="n"/>
+      <c r="Y155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z155" s="35" t="n"/>
+      <c r="AA155" s="35" t="n"/>
+      <c r="AB155" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC155" s="35" t="n"/>
+      <c r="AD155" s="35" t="n"/>
+    </row>
+    <row r="156">
+      <c r="A156" s="35" t="n"/>
+      <c r="B156" s="35" t="n"/>
+      <c r="C156" s="35" t="n"/>
+      <c r="D156" s="35" t="n"/>
+      <c r="E156" s="35" t="n"/>
+      <c r="F156" s="35" t="n"/>
+      <c r="I156" s="35" t="n"/>
+      <c r="J156" s="35" t="n"/>
+      <c r="K156" s="35" t="n"/>
+      <c r="L156" s="35" t="n"/>
+      <c r="M156" s="35" t="n"/>
+      <c r="N156" s="35" t="n"/>
+      <c r="Q156" s="35" t="n"/>
+      <c r="R156" s="35" t="n"/>
+      <c r="S156" s="35" t="n"/>
+      <c r="T156" s="35" t="n"/>
+      <c r="U156" s="35" t="n"/>
+      <c r="V156" s="35" t="n"/>
+      <c r="Y156" s="35" t="n"/>
+      <c r="Z156" s="35" t="n"/>
+      <c r="AA156" s="35" t="n"/>
+      <c r="AB156" s="35" t="n"/>
+      <c r="AC156" s="35" t="n"/>
+      <c r="AD156" s="35" t="n"/>
+    </row>
+    <row r="158">
+      <c r="A158" s="20" t="inlineStr">
+        <is>
+          <t>Court 1</t>
+        </is>
+      </c>
+      <c r="B158" s="21" t="n"/>
+      <c r="C158" s="21" t="n"/>
+      <c r="D158" s="21" t="n"/>
+      <c r="E158" s="21" t="n"/>
+      <c r="F158" s="22" t="n"/>
+      <c r="I158" s="20" t="inlineStr">
+        <is>
+          <t>Court 2</t>
+        </is>
+      </c>
+      <c r="J158" s="21" t="n"/>
+      <c r="K158" s="21" t="n"/>
+      <c r="L158" s="21" t="n"/>
+      <c r="M158" s="21" t="n"/>
+      <c r="N158" s="22" t="n"/>
+      <c r="Q158" s="20" t="inlineStr">
+        <is>
+          <t>Court 3</t>
+        </is>
+      </c>
+      <c r="R158" s="21" t="n"/>
+      <c r="S158" s="21" t="n"/>
+      <c r="T158" s="21" t="n"/>
+      <c r="U158" s="21" t="n"/>
+      <c r="V158" s="22" t="n"/>
+      <c r="Y158" s="20" t="inlineStr">
+        <is>
+          <t>Court 4</t>
+        </is>
+      </c>
+      <c r="Z158" s="21" t="n"/>
+      <c r="AA158" s="21" t="n"/>
+      <c r="AB158" s="21" t="n"/>
+      <c r="AC158" s="21" t="n"/>
+      <c r="AD158" s="22" t="n"/>
+    </row>
+    <row r="159">
+      <c r="A159" s="23" t="n"/>
+      <c r="B159" s="24" t="n"/>
+      <c r="C159" s="24" t="n"/>
+      <c r="D159" s="24" t="n"/>
+      <c r="E159" s="24" t="n"/>
+      <c r="F159" s="25" t="n"/>
+      <c r="I159" s="23" t="n"/>
+      <c r="J159" s="24" t="n"/>
+      <c r="K159" s="24" t="n"/>
+      <c r="L159" s="24" t="n"/>
+      <c r="M159" s="24" t="n"/>
+      <c r="N159" s="25" t="n"/>
+      <c r="Q159" s="23" t="n"/>
+      <c r="R159" s="24" t="n"/>
+      <c r="S159" s="24" t="n"/>
+      <c r="T159" s="24" t="n"/>
+      <c r="U159" s="24" t="n"/>
+      <c r="V159" s="25" t="n"/>
+      <c r="Y159" s="23" t="n"/>
+      <c r="Z159" s="24" t="n"/>
+      <c r="AA159" s="24" t="n"/>
+      <c r="AB159" s="24" t="n"/>
+      <c r="AC159" s="24" t="n"/>
+      <c r="AD159" s="25" t="n"/>
+    </row>
+    <row r="160">
+      <c r="B160" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="C160" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D160" s="28" t="n">
+        <v>0.5381944444444444</v>
+      </c>
+      <c r="J160" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="K160" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="L160" s="28" t="n">
+        <v>0.5381944444444444</v>
+      </c>
+      <c r="R160" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="S160" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T160" s="28" t="n">
+        <v>0.5381944444444444</v>
+      </c>
+      <c r="Z160" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Round </t>
+        </is>
+      </c>
+      <c r="AA160" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB160" s="28" t="n">
+        <v>0.5381944444444444</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Sister Sister</t>
+        </is>
+      </c>
+      <c r="B161" s="11" t="n"/>
+      <c r="C161" s="11" t="n"/>
+      <c r="D161" s="30" t="inlineStr">
+        <is>
+          <t>Next: Bracket</t>
+        </is>
+      </c>
+      <c r="E161" s="11" t="n"/>
+      <c r="F161" s="11" t="n"/>
+      <c r="I161" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Kenan &amp; Kel</t>
+        </is>
+      </c>
+      <c r="J161" s="11" t="n"/>
+      <c r="K161" s="11" t="n"/>
+      <c r="L161" s="30" t="inlineStr">
+        <is>
+          <t>Next: Bracket</t>
+        </is>
+      </c>
+      <c r="M161" s="11" t="n"/>
+      <c r="N161" s="11" t="n"/>
+      <c r="Q161" s="30" t="inlineStr">
+        <is>
+          <t>Ref: The Parkers</t>
+        </is>
+      </c>
+      <c r="R161" s="11" t="n"/>
+      <c r="S161" s="11" t="n"/>
+      <c r="T161" s="30" t="inlineStr">
+        <is>
+          <t>Next: Bracket</t>
+        </is>
+      </c>
+      <c r="U161" s="11" t="n"/>
+      <c r="V161" s="11" t="n"/>
+      <c r="Y161" s="30" t="inlineStr">
+        <is>
+          <t>Ref: Martin</t>
+        </is>
+      </c>
+      <c r="Z161" s="11" t="n"/>
+      <c r="AA161" s="11" t="n"/>
+      <c r="AB161" s="30" t="inlineStr">
+        <is>
+          <t>Next: Bracket</t>
+        </is>
+      </c>
+      <c r="AC161" s="11" t="n"/>
+      <c r="AD161" s="11" t="n"/>
+    </row>
+    <row r="162">
+      <c r="A162" s="31" t="inlineStr">
+        <is>
+          <t>Fillmore</t>
+        </is>
+      </c>
+      <c r="B162" s="11" t="n"/>
+      <c r="C162" s="11" t="n"/>
+      <c r="D162" s="31" t="inlineStr">
+        <is>
+          <t>The Incredibles</t>
+        </is>
+      </c>
+      <c r="E162" s="11" t="n"/>
+      <c r="F162" s="11" t="n"/>
+      <c r="I162" s="31" t="inlineStr">
+        <is>
+          <t>That's So Raven</t>
+        </is>
+      </c>
+      <c r="J162" s="11" t="n"/>
+      <c r="K162" s="11" t="n"/>
+      <c r="L162" s="31" t="inlineStr">
+        <is>
+          <t>Abbott Elementary</t>
+        </is>
+      </c>
+      <c r="M162" s="11" t="n"/>
+      <c r="N162" s="11" t="n"/>
+      <c r="Q162" s="31" t="inlineStr">
+        <is>
+          <t>Fresh Prince</t>
+        </is>
+      </c>
+      <c r="R162" s="11" t="n"/>
+      <c r="S162" s="11" t="n"/>
+      <c r="T162" s="31" t="inlineStr">
+        <is>
+          <t>The Boondocks</t>
+        </is>
+      </c>
+      <c r="U162" s="11" t="n"/>
+      <c r="V162" s="11" t="n"/>
+      <c r="Y162" s="31" t="inlineStr">
+        <is>
+          <t>Proud Family</t>
+        </is>
+      </c>
+      <c r="Z162" s="11" t="n"/>
+      <c r="AA162" s="11" t="n"/>
+      <c r="AB162" s="31" t="inlineStr">
+        <is>
+          <t>The Cleveland Show</t>
+        </is>
+      </c>
+      <c r="AC162" s="11" t="n"/>
+      <c r="AD162" s="11" t="n"/>
+    </row>
+    <row r="163">
+      <c r="A163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="B163" s="11" t="n"/>
+      <c r="C163" s="11" t="n"/>
+      <c r="D163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="E163" s="11" t="n"/>
+      <c r="F163" s="11" t="n"/>
+      <c r="I163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="J163" s="11" t="n"/>
+      <c r="K163" s="11" t="n"/>
+      <c r="L163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="M163" s="11" t="n"/>
+      <c r="N163" s="11" t="n"/>
+      <c r="Q163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="R163" s="11" t="n"/>
+      <c r="S163" s="11" t="n"/>
+      <c r="T163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="U163" s="11" t="n"/>
+      <c r="V163" s="11" t="n"/>
+      <c r="Y163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="Z163" s="11" t="n"/>
+      <c r="AA163" s="11" t="n"/>
+      <c r="AB163" s="32" t="inlineStr">
+        <is>
+          <t>Score</t>
+        </is>
+      </c>
+      <c r="AC163" s="11" t="n"/>
+      <c r="AD163" s="11" t="n"/>
+    </row>
+    <row r="164">
+      <c r="A164" s="11" t="n"/>
+      <c r="B164" s="11" t="n"/>
+      <c r="C164" s="11" t="n"/>
+      <c r="D164" s="11" t="n"/>
+      <c r="E164" s="11" t="n"/>
+      <c r="F164" s="11" t="n"/>
+      <c r="I164" s="11" t="n"/>
+      <c r="J164" s="11" t="n"/>
+      <c r="K164" s="11" t="n"/>
+      <c r="L164" s="11" t="n"/>
+      <c r="M164" s="11" t="n"/>
+      <c r="N164" s="11" t="n"/>
+      <c r="Q164" s="11" t="n"/>
+      <c r="R164" s="11" t="n"/>
+      <c r="S164" s="11" t="n"/>
+      <c r="T164" s="11" t="n"/>
+      <c r="U164" s="11" t="n"/>
+      <c r="V164" s="11" t="n"/>
+      <c r="Y164" s="11" t="n"/>
+      <c r="Z164" s="11" t="n"/>
+      <c r="AA164" s="11" t="n"/>
+      <c r="AB164" s="11" t="n"/>
+      <c r="AC164" s="11" t="n"/>
+      <c r="AD164" s="11" t="n"/>
+    </row>
+    <row r="165">
+      <c r="A165" s="11" t="n"/>
+      <c r="B165" s="11" t="n"/>
+      <c r="C165" s="11" t="n"/>
+      <c r="D165" s="11" t="n"/>
+      <c r="E165" s="11" t="n"/>
+      <c r="F165" s="11" t="n"/>
+      <c r="I165" s="11" t="n"/>
+      <c r="J165" s="11" t="n"/>
+      <c r="K165" s="11" t="n"/>
+      <c r="L165" s="11" t="n"/>
+      <c r="M165" s="11" t="n"/>
+      <c r="N165" s="11" t="n"/>
+      <c r="Q165" s="11" t="n"/>
+      <c r="R165" s="11" t="n"/>
+      <c r="S165" s="11" t="n"/>
+      <c r="T165" s="11" t="n"/>
+      <c r="U165" s="11" t="n"/>
+      <c r="V165" s="11" t="n"/>
+      <c r="Y165" s="11" t="n"/>
+      <c r="Z165" s="11" t="n"/>
+      <c r="AA165" s="11" t="n"/>
+      <c r="AB165" s="11" t="n"/>
+      <c r="AC165" s="11" t="n"/>
+      <c r="AD165" s="11" t="n"/>
+    </row>
+    <row r="166">
+      <c r="A166" s="11" t="n"/>
+      <c r="B166" s="11" t="n"/>
+      <c r="C166" s="11" t="n"/>
+      <c r="D166" s="11" t="n"/>
+      <c r="E166" s="11" t="n"/>
+      <c r="F166" s="11" t="n"/>
+      <c r="I166" s="11" t="n"/>
+      <c r="J166" s="11" t="n"/>
+      <c r="K166" s="11" t="n"/>
+      <c r="L166" s="11" t="n"/>
+      <c r="M166" s="11" t="n"/>
+      <c r="N166" s="11" t="n"/>
+      <c r="Q166" s="11" t="n"/>
+      <c r="R166" s="11" t="n"/>
+      <c r="S166" s="11" t="n"/>
+      <c r="T166" s="11" t="n"/>
+      <c r="U166" s="11" t="n"/>
+      <c r="V166" s="11" t="n"/>
+      <c r="Y166" s="11" t="n"/>
+      <c r="Z166" s="11" t="n"/>
+      <c r="AA166" s="11" t="n"/>
+      <c r="AB166" s="11" t="n"/>
+      <c r="AC166" s="11" t="n"/>
+      <c r="AD166" s="11" t="n"/>
+    </row>
+    <row r="167">
+      <c r="A167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Bracket</t>
+        </is>
+      </c>
+      <c r="B167" s="11" t="n"/>
+      <c r="C167" s="11" t="n"/>
+      <c r="D167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Bracket</t>
+        </is>
+      </c>
+      <c r="E167" s="11" t="n"/>
+      <c r="F167" s="11" t="n"/>
+      <c r="I167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Bracket</t>
+        </is>
+      </c>
+      <c r="J167" s="11" t="n"/>
+      <c r="K167" s="11" t="n"/>
+      <c r="L167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Bracket</t>
+        </is>
+      </c>
+      <c r="M167" s="11" t="n"/>
+      <c r="N167" s="11" t="n"/>
+      <c r="Q167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Bracket</t>
+        </is>
+      </c>
+      <c r="R167" s="11" t="n"/>
+      <c r="S167" s="11" t="n"/>
+      <c r="T167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Bracket</t>
+        </is>
+      </c>
+      <c r="U167" s="11" t="n"/>
+      <c r="V167" s="11" t="n"/>
+      <c r="Y167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next:  Bracket</t>
+        </is>
+      </c>
+      <c r="Z167" s="11" t="n"/>
+      <c r="AA167" s="11" t="n"/>
+      <c r="AB167" s="33" t="inlineStr">
+        <is>
+          <t>Where to next: Bracket</t>
+        </is>
+      </c>
+      <c r="AC167" s="11" t="n"/>
+      <c r="AD167" s="11" t="n"/>
+    </row>
+    <row r="168">
+      <c r="A168" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="B168" s="11" t="n"/>
+      <c r="C168" s="11" t="n"/>
+      <c r="D168" s="11" t="n"/>
+      <c r="E168" s="11" t="n"/>
+      <c r="F168" s="11" t="n"/>
+      <c r="I168" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="J168" s="11" t="n"/>
+      <c r="K168" s="11" t="n"/>
+      <c r="L168" s="11" t="n"/>
+      <c r="M168" s="11" t="n"/>
+      <c r="N168" s="11" t="n"/>
+      <c r="Q168" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="R168" s="11" t="n"/>
+      <c r="S168" s="11" t="n"/>
+      <c r="T168" s="11" t="n"/>
+      <c r="U168" s="11" t="n"/>
+      <c r="V168" s="11" t="n"/>
+      <c r="Y168" s="30" t="inlineStr">
+        <is>
+          <t>Comments:</t>
+        </is>
+      </c>
+      <c r="Z168" s="11" t="n"/>
+      <c r="AA168" s="11" t="n"/>
+      <c r="AB168" s="11" t="n"/>
+      <c r="AC168" s="11" t="n"/>
+      <c r="AD168" s="11" t="n"/>
+    </row>
+    <row r="169">
+      <c r="A169" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="B169" s="11" t="n"/>
+      <c r="C169" s="11" t="n"/>
+      <c r="D169" s="11" t="n"/>
+      <c r="E169" s="11" t="n"/>
+      <c r="F169" s="11" t="n"/>
+      <c r="I169" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="J169" s="11" t="n"/>
+      <c r="K169" s="11" t="n"/>
+      <c r="L169" s="11" t="n"/>
+      <c r="M169" s="11" t="n"/>
+      <c r="N169" s="11" t="n"/>
+      <c r="Q169" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="R169" s="11" t="n"/>
+      <c r="S169" s="11" t="n"/>
+      <c r="T169" s="11" t="n"/>
+      <c r="U169" s="11" t="n"/>
+      <c r="V169" s="11" t="n"/>
+      <c r="Y169" s="30" t="inlineStr">
+        <is>
+          <t>Penalties or cards:</t>
+        </is>
+      </c>
+      <c r="Z169" s="11" t="n"/>
+      <c r="AA169" s="11" t="n"/>
+      <c r="AB169" s="11" t="n"/>
+      <c r="AC169" s="11" t="n"/>
+      <c r="AD169" s="11" t="n"/>
+    </row>
+    <row r="170">
+      <c r="A170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="B170" s="11" t="n"/>
+      <c r="C170" s="11" t="n"/>
+      <c r="D170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="E170" s="11" t="n"/>
+      <c r="F170" s="11" t="n"/>
+      <c r="I170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="J170" s="11" t="n"/>
+      <c r="K170" s="11" t="n"/>
+      <c r="L170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="M170" s="11" t="n"/>
+      <c r="N170" s="11" t="n"/>
+      <c r="Q170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="R170" s="11" t="n"/>
+      <c r="S170" s="11" t="n"/>
+      <c r="T170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="U170" s="11" t="n"/>
+      <c r="V170" s="11" t="n"/>
+      <c r="Y170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="Z170" s="11" t="n"/>
+      <c r="AA170" s="11" t="n"/>
+      <c r="AB170" s="32" t="inlineStr">
+        <is>
+          <t>Signatures</t>
+        </is>
+      </c>
+      <c r="AC170" s="11" t="n"/>
+      <c r="AD170" s="11" t="n"/>
+    </row>
+    <row r="171">
+      <c r="A171" s="11" t="n"/>
+      <c r="B171" s="11" t="n"/>
+      <c r="C171" s="11" t="n"/>
+      <c r="D171" s="11" t="n"/>
+      <c r="E171" s="11" t="n"/>
+      <c r="F171" s="11" t="n"/>
+      <c r="I171" s="11" t="n"/>
+      <c r="J171" s="11" t="n"/>
+      <c r="K171" s="11" t="n"/>
+      <c r="L171" s="11" t="n"/>
+      <c r="M171" s="11" t="n"/>
+      <c r="N171" s="11" t="n"/>
+      <c r="Q171" s="11" t="n"/>
+      <c r="R171" s="11" t="n"/>
+      <c r="S171" s="11" t="n"/>
+      <c r="T171" s="11" t="n"/>
+      <c r="U171" s="11" t="n"/>
+      <c r="V171" s="11" t="n"/>
+      <c r="Y171" s="11" t="n"/>
+      <c r="Z171" s="11" t="n"/>
+      <c r="AA171" s="11" t="n"/>
+      <c r="AB171" s="11" t="n"/>
+      <c r="AC171" s="11" t="n"/>
+      <c r="AD171" s="11" t="n"/>
+    </row>
+    <row r="172">
+      <c r="A172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="B172" s="35" t="n"/>
+      <c r="C172" s="35" t="n"/>
+      <c r="D172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="E172" s="35" t="n"/>
+      <c r="F172" s="35" t="n"/>
+      <c r="I172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="J172" s="35" t="n"/>
+      <c r="K172" s="35" t="n"/>
+      <c r="L172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="M172" s="35" t="n"/>
+      <c r="N172" s="35" t="n"/>
+      <c r="Q172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="R172" s="35" t="n"/>
+      <c r="S172" s="35" t="n"/>
+      <c r="T172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="U172" s="35" t="n"/>
+      <c r="V172" s="35" t="n"/>
+      <c r="Y172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="Z172" s="35" t="n"/>
+      <c r="AA172" s="35" t="n"/>
+      <c r="AB172" s="34" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Player: </t>
+        </is>
+      </c>
+      <c r="AC172" s="35" t="n"/>
+      <c r="AD172" s="35" t="n"/>
+    </row>
+    <row r="173">
+      <c r="A173" s="35" t="n"/>
+      <c r="B173" s="35" t="n"/>
+      <c r="C173" s="35" t="n"/>
+      <c r="D173" s="35" t="n"/>
+      <c r="E173" s="35" t="n"/>
+      <c r="F173" s="35" t="n"/>
+      <c r="I173" s="35" t="n"/>
+      <c r="J173" s="35" t="n"/>
+      <c r="K173" s="35" t="n"/>
+      <c r="L173" s="35" t="n"/>
+      <c r="M173" s="35" t="n"/>
+      <c r="N173" s="35" t="n"/>
+      <c r="Q173" s="35" t="n"/>
+      <c r="R173" s="35" t="n"/>
+      <c r="S173" s="35" t="n"/>
+      <c r="T173" s="35" t="n"/>
+      <c r="U173" s="35" t="n"/>
+      <c r="V173" s="35" t="n"/>
+      <c r="Y173" s="35" t="n"/>
+      <c r="Z173" s="35" t="n"/>
+      <c r="AA173" s="35" t="n"/>
+      <c r="AB173" s="35" t="n"/>
+      <c r="AC173" s="35" t="n"/>
+      <c r="AD173" s="35" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="600">
+    <mergeCell ref="Y32:AA33"/>
+    <mergeCell ref="A133:F133"/>
+    <mergeCell ref="D85:F86"/>
+    <mergeCell ref="L126:N126"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="I56:K56"/>
+    <mergeCell ref="I127:K127"/>
+    <mergeCell ref="T110:V110"/>
+    <mergeCell ref="Y40:AA40"/>
+    <mergeCell ref="A15:C16"/>
+    <mergeCell ref="A57:C57"/>
+    <mergeCell ref="L67:N68"/>
+    <mergeCell ref="Q80:S80"/>
+    <mergeCell ref="A30:C31"/>
+    <mergeCell ref="Y28:AD28"/>
+    <mergeCell ref="I169:N169"/>
+    <mergeCell ref="A158:F159"/>
+    <mergeCell ref="Y1:AD2"/>
+    <mergeCell ref="Y91:AA91"/>
+    <mergeCell ref="I71:N72"/>
+    <mergeCell ref="Q91:S91"/>
+    <mergeCell ref="D13:F14"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="T57:V57"/>
+    <mergeCell ref="Y47:AD47"/>
+    <mergeCell ref="A64:F64"/>
+    <mergeCell ref="Q47:V47"/>
+    <mergeCell ref="AB127:AD127"/>
+    <mergeCell ref="A82:F82"/>
+    <mergeCell ref="Q93:S96"/>
+    <mergeCell ref="A110:C110"/>
+    <mergeCell ref="I93:K96"/>
+    <mergeCell ref="D15:F16"/>
+    <mergeCell ref="I67:K68"/>
+    <mergeCell ref="L97:N97"/>
+    <mergeCell ref="L6:N9"/>
+    <mergeCell ref="I115:K115"/>
+    <mergeCell ref="Q63:V63"/>
+    <mergeCell ref="AB137:AD138"/>
+    <mergeCell ref="AB56:AD56"/>
+    <mergeCell ref="Q109:S109"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I117:N117"/>
+    <mergeCell ref="Q22:S22"/>
+    <mergeCell ref="Y15:AA16"/>
+    <mergeCell ref="D155:F156"/>
+    <mergeCell ref="AB57:AD57"/>
+    <mergeCell ref="D74:F74"/>
+    <mergeCell ref="I4:K4"/>
+    <mergeCell ref="A153:C154"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="Y30:AA31"/>
+    <mergeCell ref="T83:V84"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="D5:F5"/>
+    <mergeCell ref="D132:F132"/>
+    <mergeCell ref="A128:C131"/>
+    <mergeCell ref="A65:C66"/>
+    <mergeCell ref="Y137:AA138"/>
+    <mergeCell ref="T126:V126"/>
+    <mergeCell ref="Y56:AA56"/>
+    <mergeCell ref="Q116:V116"/>
+    <mergeCell ref="I46:N46"/>
+    <mergeCell ref="Y134:AD134"/>
+    <mergeCell ref="AB67:AD68"/>
+    <mergeCell ref="A85:C86"/>
+    <mergeCell ref="A23:C26"/>
+    <mergeCell ref="AB4:AD4"/>
+    <mergeCell ref="Y74:AA74"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="AB75:AD75"/>
+    <mergeCell ref="L85:N86"/>
+    <mergeCell ref="Q117:V117"/>
+    <mergeCell ref="Y170:AA171"/>
+    <mergeCell ref="Y98:AD98"/>
+    <mergeCell ref="T80:V80"/>
+    <mergeCell ref="D30:F31"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="I75:K75"/>
+    <mergeCell ref="I153:K154"/>
+    <mergeCell ref="Y132:AA132"/>
+    <mergeCell ref="T144:V144"/>
+    <mergeCell ref="Y41:AA44"/>
+    <mergeCell ref="A58:C61"/>
+    <mergeCell ref="A126:C126"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="A150:C150"/>
+    <mergeCell ref="L40:N40"/>
+    <mergeCell ref="I110:K110"/>
+    <mergeCell ref="A144:C144"/>
+    <mergeCell ref="Y67:AA68"/>
+    <mergeCell ref="Y93:AA96"/>
+    <mergeCell ref="I135:K136"/>
+    <mergeCell ref="A50:C51"/>
+    <mergeCell ref="I85:K86"/>
+    <mergeCell ref="AB41:AD44"/>
+    <mergeCell ref="AB153:AD154"/>
+    <mergeCell ref="T146:V149"/>
+    <mergeCell ref="D170:F171"/>
+    <mergeCell ref="Q133:V133"/>
+    <mergeCell ref="I11:N11"/>
+    <mergeCell ref="I133:N133"/>
+    <mergeCell ref="T58:V61"/>
+    <mergeCell ref="A18:F19"/>
+    <mergeCell ref="T85:V86"/>
+    <mergeCell ref="Q62:S62"/>
+    <mergeCell ref="Y62:AA62"/>
+    <mergeCell ref="Y117:AD117"/>
+    <mergeCell ref="Q127:S127"/>
+    <mergeCell ref="AB110:AD110"/>
+    <mergeCell ref="I57:K57"/>
+    <mergeCell ref="A155:C156"/>
+    <mergeCell ref="L5:N5"/>
+    <mergeCell ref="A74:C74"/>
+    <mergeCell ref="Q128:S131"/>
+    <mergeCell ref="L132:N132"/>
+    <mergeCell ref="A145:C145"/>
+    <mergeCell ref="I128:K131"/>
+    <mergeCell ref="I65:K66"/>
+    <mergeCell ref="A170:C171"/>
+    <mergeCell ref="L161:N161"/>
+    <mergeCell ref="Q46:V46"/>
+    <mergeCell ref="Y81:AD81"/>
+    <mergeCell ref="I158:N159"/>
+    <mergeCell ref="A172:C173"/>
+    <mergeCell ref="Q71:V72"/>
+    <mergeCell ref="L13:N14"/>
+    <mergeCell ref="L144:N144"/>
+    <mergeCell ref="T48:V49"/>
+    <mergeCell ref="I64:N64"/>
+    <mergeCell ref="I82:N82"/>
+    <mergeCell ref="AB85:AD86"/>
+    <mergeCell ref="L21:N21"/>
+    <mergeCell ref="L15:N16"/>
+    <mergeCell ref="Q67:S68"/>
+    <mergeCell ref="D120:F121"/>
+    <mergeCell ref="Q57:S57"/>
+    <mergeCell ref="T145:V145"/>
+    <mergeCell ref="Y75:AA75"/>
+    <mergeCell ref="L30:N31"/>
+    <mergeCell ref="A92:C92"/>
+    <mergeCell ref="I18:N19"/>
+    <mergeCell ref="Q118:S119"/>
+    <mergeCell ref="Q115:S115"/>
+    <mergeCell ref="I155:K156"/>
+    <mergeCell ref="Y63:AD63"/>
+    <mergeCell ref="A45:C45"/>
+    <mergeCell ref="I126:K126"/>
+    <mergeCell ref="A100:C101"/>
+    <mergeCell ref="Q39:S39"/>
+    <mergeCell ref="I13:K14"/>
+    <mergeCell ref="Y135:AA136"/>
+    <mergeCell ref="L155:N156"/>
+    <mergeCell ref="Y36:AD37"/>
+    <mergeCell ref="A53:F54"/>
+    <mergeCell ref="L74:N74"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="AB128:AD131"/>
+    <mergeCell ref="T92:V92"/>
+    <mergeCell ref="Q162:S162"/>
+    <mergeCell ref="AB146:AD149"/>
+    <mergeCell ref="L170:N171"/>
+    <mergeCell ref="I12:N12"/>
+    <mergeCell ref="AB83:AD84"/>
+    <mergeCell ref="D100:F101"/>
+    <mergeCell ref="L135:N136"/>
+    <mergeCell ref="D50:F51"/>
+    <mergeCell ref="AB58:AD61"/>
+    <mergeCell ref="AB126:AD126"/>
+    <mergeCell ref="L167:N167"/>
+    <mergeCell ref="A81:F81"/>
+    <mergeCell ref="A152:F152"/>
+    <mergeCell ref="D6:F9"/>
+    <mergeCell ref="I10:K10"/>
+    <mergeCell ref="D32:F33"/>
+    <mergeCell ref="Q155:S156"/>
+    <mergeCell ref="I74:K74"/>
+    <mergeCell ref="Q170:S171"/>
+    <mergeCell ref="AB80:AD80"/>
+    <mergeCell ref="Y50:AA51"/>
+    <mergeCell ref="I146:K149"/>
+    <mergeCell ref="D80:F80"/>
+    <mergeCell ref="A76:C79"/>
+    <mergeCell ref="L100:N101"/>
+    <mergeCell ref="I88:N89"/>
+    <mergeCell ref="Q123:V124"/>
+    <mergeCell ref="T13:V14"/>
+    <mergeCell ref="AB144:AD144"/>
+    <mergeCell ref="Q64:V64"/>
+    <mergeCell ref="I58:K61"/>
+    <mergeCell ref="Y82:AD82"/>
+    <mergeCell ref="A99:F99"/>
+    <mergeCell ref="A163:C166"/>
+    <mergeCell ref="D27:F27"/>
+    <mergeCell ref="Q150:S150"/>
+    <mergeCell ref="I150:K150"/>
+    <mergeCell ref="T15:V16"/>
+    <mergeCell ref="T120:V121"/>
+    <mergeCell ref="L120:N121"/>
+    <mergeCell ref="Y22:AA22"/>
+    <mergeCell ref="D91:F91"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="I92:K92"/>
+    <mergeCell ref="AB145:AD145"/>
+    <mergeCell ref="I15:K16"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="Y80:AA80"/>
+    <mergeCell ref="I30:K31"/>
+    <mergeCell ref="A97:C97"/>
+    <mergeCell ref="Q11:V11"/>
+    <mergeCell ref="A161:C161"/>
+    <mergeCell ref="T115:V115"/>
+    <mergeCell ref="Q169:V169"/>
+    <mergeCell ref="L115:N115"/>
+    <mergeCell ref="AB155:AD156"/>
+    <mergeCell ref="I53:N54"/>
+    <mergeCell ref="Y4:AA4"/>
+    <mergeCell ref="T39:V39"/>
+    <mergeCell ref="AB92:AD92"/>
+    <mergeCell ref="Y162:AA162"/>
+    <mergeCell ref="D109:F109"/>
+    <mergeCell ref="T163:V166"/>
+    <mergeCell ref="AB170:AD171"/>
+    <mergeCell ref="Q12:V12"/>
+    <mergeCell ref="T135:V136"/>
+    <mergeCell ref="AB5:AD5"/>
+    <mergeCell ref="I151:N151"/>
+    <mergeCell ref="T5:V5"/>
+    <mergeCell ref="Y128:AA131"/>
+    <mergeCell ref="L76:N79"/>
+    <mergeCell ref="I145:K145"/>
+    <mergeCell ref="Q65:S66"/>
+    <mergeCell ref="D40:F40"/>
+    <mergeCell ref="T97:V97"/>
+    <mergeCell ref="D118:F119"/>
+    <mergeCell ref="I170:K171"/>
+    <mergeCell ref="L163:N166"/>
+    <mergeCell ref="AB150:AD150"/>
+    <mergeCell ref="A46:F46"/>
+    <mergeCell ref="I172:K173"/>
+    <mergeCell ref="T6:V9"/>
+    <mergeCell ref="Y10:AA10"/>
+    <mergeCell ref="D150:F150"/>
+    <mergeCell ref="Q10:S10"/>
+    <mergeCell ref="T32:V33"/>
+    <mergeCell ref="T21:V21"/>
+    <mergeCell ref="Y109:AA109"/>
+    <mergeCell ref="T30:V31"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="Q146:S149"/>
+    <mergeCell ref="Y118:AA119"/>
+    <mergeCell ref="L32:N33"/>
+    <mergeCell ref="Y123:AD124"/>
+    <mergeCell ref="T65:V66"/>
+    <mergeCell ref="Q58:S61"/>
+    <mergeCell ref="T27:V27"/>
+    <mergeCell ref="I163:K166"/>
+    <mergeCell ref="I99:N99"/>
+    <mergeCell ref="L27:N27"/>
+    <mergeCell ref="I100:K101"/>
+    <mergeCell ref="I106:N107"/>
+    <mergeCell ref="A167:C167"/>
+    <mergeCell ref="Y150:AA150"/>
+    <mergeCell ref="T91:V91"/>
+    <mergeCell ref="L91:N91"/>
+    <mergeCell ref="Q21:S21"/>
+    <mergeCell ref="I102:K103"/>
+    <mergeCell ref="Q15:S16"/>
+    <mergeCell ref="A168:F168"/>
+    <mergeCell ref="D93:F96"/>
+    <mergeCell ref="A162:C162"/>
+    <mergeCell ref="I23:K26"/>
+    <mergeCell ref="Q30:S31"/>
+    <mergeCell ref="L50:N51"/>
+    <mergeCell ref="Y11:AD11"/>
+    <mergeCell ref="Y18:AD19"/>
+    <mergeCell ref="AB115:AD115"/>
+    <mergeCell ref="Y111:AA114"/>
+    <mergeCell ref="Y169:AD169"/>
+    <mergeCell ref="T167:V167"/>
+    <mergeCell ref="Y48:AA49"/>
+    <mergeCell ref="L45:N45"/>
+    <mergeCell ref="Q48:S49"/>
+    <mergeCell ref="Q153:S154"/>
+    <mergeCell ref="A83:C84"/>
+    <mergeCell ref="I152:N152"/>
+    <mergeCell ref="AB39:AD39"/>
+    <mergeCell ref="L109:N109"/>
+    <mergeCell ref="D62:F62"/>
+    <mergeCell ref="A1:F2"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="D56:F56"/>
+    <mergeCell ref="Q74:S74"/>
+    <mergeCell ref="D127:F127"/>
+    <mergeCell ref="T75:V75"/>
+    <mergeCell ref="Q110:S110"/>
+    <mergeCell ref="AB97:AD97"/>
+    <mergeCell ref="A109:C109"/>
+    <mergeCell ref="L118:N119"/>
+    <mergeCell ref="Q135:S136"/>
+    <mergeCell ref="L80:N80"/>
+    <mergeCell ref="I76:K79"/>
+    <mergeCell ref="AB163:AD166"/>
+    <mergeCell ref="Y172:AA173"/>
+    <mergeCell ref="A118:C119"/>
+    <mergeCell ref="Y116:AD116"/>
+    <mergeCell ref="D111:F114"/>
+    <mergeCell ref="AB120:AD121"/>
+    <mergeCell ref="D137:F138"/>
+    <mergeCell ref="L172:N173"/>
+    <mergeCell ref="A141:F142"/>
+    <mergeCell ref="T23:V26"/>
+    <mergeCell ref="Q92:S92"/>
+    <mergeCell ref="Y127:AA127"/>
+    <mergeCell ref="D41:F44"/>
+    <mergeCell ref="D67:F68"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="Y163:AA166"/>
+    <mergeCell ref="AB27:AD27"/>
+    <mergeCell ref="Q100:S101"/>
+    <mergeCell ref="D75:F75"/>
+    <mergeCell ref="T132:V132"/>
+    <mergeCell ref="I161:K161"/>
+    <mergeCell ref="I6:K9"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A111:C114"/>
+    <mergeCell ref="Y46:AD46"/>
+    <mergeCell ref="Y53:AD54"/>
+    <mergeCell ref="Q53:V54"/>
+    <mergeCell ref="Q158:V159"/>
+    <mergeCell ref="A137:C138"/>
+    <mergeCell ref="Y71:AD72"/>
+    <mergeCell ref="A88:F89"/>
+    <mergeCell ref="D39:F39"/>
+    <mergeCell ref="Y12:AD12"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A36:F37"/>
+    <mergeCell ref="A134:F134"/>
+    <mergeCell ref="AB135:AD136"/>
+    <mergeCell ref="T50:V51"/>
+    <mergeCell ref="AB167:AD167"/>
+    <mergeCell ref="Y153:AA154"/>
+    <mergeCell ref="I168:N168"/>
+    <mergeCell ref="L93:N96"/>
+    <mergeCell ref="Q23:S26"/>
+    <mergeCell ref="I83:K84"/>
+    <mergeCell ref="Y115:AA115"/>
+    <mergeCell ref="A132:C132"/>
+    <mergeCell ref="I45:K45"/>
+    <mergeCell ref="Q126:S126"/>
+    <mergeCell ref="Y39:AA39"/>
+    <mergeCell ref="AB40:AD40"/>
+    <mergeCell ref="D57:F57"/>
+    <mergeCell ref="I22:K22"/>
+    <mergeCell ref="Q76:S79"/>
+    <mergeCell ref="T155:V156"/>
+    <mergeCell ref="T74:V74"/>
+    <mergeCell ref="AB65:AD66"/>
+    <mergeCell ref="T170:V171"/>
+    <mergeCell ref="T40:V40"/>
+    <mergeCell ref="L111:N114"/>
+    <mergeCell ref="Q99:V99"/>
+    <mergeCell ref="Q163:S166"/>
+    <mergeCell ref="A151:F151"/>
+    <mergeCell ref="I167:K167"/>
+    <mergeCell ref="D153:F154"/>
+    <mergeCell ref="L137:N138"/>
+    <mergeCell ref="T172:V173"/>
+    <mergeCell ref="Q141:V142"/>
+    <mergeCell ref="Q102:S103"/>
+    <mergeCell ref="Q144:S144"/>
+    <mergeCell ref="Y57:AA57"/>
+    <mergeCell ref="Q45:S45"/>
+    <mergeCell ref="T93:V96"/>
+    <mergeCell ref="D110:F110"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="D135:F136"/>
+    <mergeCell ref="T45:V45"/>
+    <mergeCell ref="Y133:AD133"/>
+    <mergeCell ref="Y158:AD159"/>
+    <mergeCell ref="AB13:AD14"/>
+    <mergeCell ref="Y64:AD64"/>
+    <mergeCell ref="T62:V62"/>
+    <mergeCell ref="I134:N134"/>
+    <mergeCell ref="L62:N62"/>
+    <mergeCell ref="I1:N2"/>
+    <mergeCell ref="A106:F107"/>
+    <mergeCell ref="L127:N127"/>
+    <mergeCell ref="T102:V103"/>
+    <mergeCell ref="Y110:AA110"/>
+    <mergeCell ref="AB15:AD16"/>
+    <mergeCell ref="L4:N4"/>
+    <mergeCell ref="L162:N162"/>
+    <mergeCell ref="A102:C103"/>
+    <mergeCell ref="AB93:AD96"/>
+    <mergeCell ref="Y23:AA26"/>
+    <mergeCell ref="Q27:S27"/>
+    <mergeCell ref="I5:K5"/>
+    <mergeCell ref="D128:F131"/>
+    <mergeCell ref="I132:K132"/>
+    <mergeCell ref="D65:F66"/>
+    <mergeCell ref="Y45:AA45"/>
+    <mergeCell ref="A62:C62"/>
+    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="Q18:V19"/>
+    <mergeCell ref="AB10:AD10"/>
+    <mergeCell ref="I141:N142"/>
+    <mergeCell ref="AB74:AD74"/>
+    <mergeCell ref="Q85:S86"/>
+    <mergeCell ref="A120:C121"/>
+    <mergeCell ref="L57:N57"/>
+    <mergeCell ref="T100:V101"/>
+    <mergeCell ref="Q151:V151"/>
+    <mergeCell ref="D22:F22"/>
+    <mergeCell ref="L41:N44"/>
+    <mergeCell ref="L75:N75"/>
+    <mergeCell ref="L153:N154"/>
+    <mergeCell ref="D146:F149"/>
+    <mergeCell ref="T76:V79"/>
+    <mergeCell ref="Q145:S145"/>
+    <mergeCell ref="Y65:AA66"/>
+    <mergeCell ref="AB132:AD132"/>
+    <mergeCell ref="Q6:S9"/>
+    <mergeCell ref="I47:N47"/>
+    <mergeCell ref="I111:K114"/>
+    <mergeCell ref="D58:F61"/>
+    <mergeCell ref="I137:K138"/>
+    <mergeCell ref="Q172:S173"/>
+    <mergeCell ref="D126:F126"/>
+    <mergeCell ref="A56:C56"/>
+    <mergeCell ref="A27:C27"/>
+    <mergeCell ref="L39:N39"/>
+    <mergeCell ref="Q40:S40"/>
+    <mergeCell ref="AB21:AD21"/>
+    <mergeCell ref="D4:F4"/>
+    <mergeCell ref="AB30:AD31"/>
+    <mergeCell ref="Y146:AA149"/>
+    <mergeCell ref="Y83:AA84"/>
+    <mergeCell ref="Q83:S84"/>
+    <mergeCell ref="Y88:AD89"/>
+    <mergeCell ref="T161:V161"/>
+    <mergeCell ref="AB62:AD62"/>
+    <mergeCell ref="Y58:AA61"/>
+    <mergeCell ref="Y85:AA86"/>
+    <mergeCell ref="Q1:V2"/>
+    <mergeCell ref="Y126:AA126"/>
+    <mergeCell ref="A71:F72"/>
+    <mergeCell ref="D48:F49"/>
+    <mergeCell ref="A41:C44"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="A6:C9"/>
+    <mergeCell ref="Q137:S138"/>
+    <mergeCell ref="A32:C33"/>
+    <mergeCell ref="T128:V131"/>
+    <mergeCell ref="L65:N66"/>
+    <mergeCell ref="Q97:S97"/>
+    <mergeCell ref="A80:C80"/>
+    <mergeCell ref="AB172:AD173"/>
+    <mergeCell ref="I28:N28"/>
+    <mergeCell ref="Y141:AD142"/>
+    <mergeCell ref="Y144:AA144"/>
+    <mergeCell ref="Q13:S14"/>
+    <mergeCell ref="Q152:V152"/>
+    <mergeCell ref="T109:V109"/>
+    <mergeCell ref="I120:K121"/>
+    <mergeCell ref="T22:V22"/>
+    <mergeCell ref="Y145:AA145"/>
+    <mergeCell ref="A91:C91"/>
+    <mergeCell ref="D92:F92"/>
+    <mergeCell ref="L83:N84"/>
+    <mergeCell ref="T118:V119"/>
+    <mergeCell ref="Q111:S114"/>
+    <mergeCell ref="I41:K44"/>
+    <mergeCell ref="A146:C149"/>
+    <mergeCell ref="AB100:AD101"/>
+    <mergeCell ref="Q56:S56"/>
+    <mergeCell ref="Q88:V89"/>
+    <mergeCell ref="I81:N81"/>
+    <mergeCell ref="Q134:V134"/>
+    <mergeCell ref="AB102:AD103"/>
+    <mergeCell ref="Y155:AA156"/>
+    <mergeCell ref="T4:V4"/>
+    <mergeCell ref="T162:V162"/>
+    <mergeCell ref="AB23:AD26"/>
+    <mergeCell ref="Y92:AA92"/>
+    <mergeCell ref="Y5:AA5"/>
+    <mergeCell ref="Q5:S5"/>
+    <mergeCell ref="L128:N131"/>
+    <mergeCell ref="Q132:S132"/>
+    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="I50:K51"/>
+    <mergeCell ref="Y100:AA101"/>
+    <mergeCell ref="Q167:S167"/>
+    <mergeCell ref="Q161:S161"/>
+    <mergeCell ref="Q41:S44"/>
+    <mergeCell ref="D172:F173"/>
+    <mergeCell ref="L10:N10"/>
+    <mergeCell ref="Y102:AA103"/>
+    <mergeCell ref="A48:C49"/>
+    <mergeCell ref="I32:K33"/>
+    <mergeCell ref="I29:N29"/>
+    <mergeCell ref="I36:N37"/>
+    <mergeCell ref="Y151:AD151"/>
+    <mergeCell ref="AB76:AD79"/>
+    <mergeCell ref="AB50:AD51"/>
+    <mergeCell ref="L146:N149"/>
+    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="L58:N61"/>
+    <mergeCell ref="Y152:AD152"/>
+    <mergeCell ref="A98:F98"/>
+    <mergeCell ref="D163:F166"/>
+    <mergeCell ref="A169:F169"/>
+    <mergeCell ref="T150:V150"/>
+    <mergeCell ref="I27:K27"/>
+    <mergeCell ref="L150:N150"/>
+    <mergeCell ref="D102:F103"/>
+    <mergeCell ref="I91:K91"/>
+    <mergeCell ref="Y76:AA79"/>
+    <mergeCell ref="D23:F26"/>
+    <mergeCell ref="D97:F97"/>
+    <mergeCell ref="A93:C96"/>
+    <mergeCell ref="AB161:AD161"/>
+    <mergeCell ref="Q81:V81"/>
+    <mergeCell ref="AB6:AD9"/>
+    <mergeCell ref="T111:V114"/>
+    <mergeCell ref="Y99:AD99"/>
+    <mergeCell ref="Y106:AD107"/>
+    <mergeCell ref="A116:F116"/>
+    <mergeCell ref="A123:F124"/>
+    <mergeCell ref="L48:N49"/>
+    <mergeCell ref="Q106:V107"/>
+    <mergeCell ref="AB32:AD33"/>
+    <mergeCell ref="T137:V138"/>
+    <mergeCell ref="T56:V56"/>
+    <mergeCell ref="L56:N56"/>
+    <mergeCell ref="AB162:AD162"/>
+    <mergeCell ref="I109:K109"/>
+    <mergeCell ref="A117:F117"/>
+    <mergeCell ref="L145:N145"/>
+    <mergeCell ref="Q75:S75"/>
+    <mergeCell ref="Q168:V168"/>
+    <mergeCell ref="A127:C127"/>
+    <mergeCell ref="L110:N110"/>
+    <mergeCell ref="Y97:AA97"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="D115:F115"/>
+    <mergeCell ref="I118:K119"/>
+    <mergeCell ref="D76:F79"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="Y161:AA161"/>
+    <mergeCell ref="Q28:V28"/>
+    <mergeCell ref="Y6:AA9"/>
+    <mergeCell ref="Y13:AA14"/>
+    <mergeCell ref="AB45:AD45"/>
+    <mergeCell ref="I144:K144"/>
+    <mergeCell ref="A13:C14"/>
+    <mergeCell ref="D45:F45"/>
+    <mergeCell ref="I48:K49"/>
+    <mergeCell ref="AB91:AD91"/>
+    <mergeCell ref="Y21:AA21"/>
+    <mergeCell ref="AB109:AD109"/>
+    <mergeCell ref="Y29:AD29"/>
+    <mergeCell ref="Y120:AA121"/>
+    <mergeCell ref="Q29:V29"/>
+    <mergeCell ref="Q36:V37"/>
+    <mergeCell ref="Q120:S121"/>
+    <mergeCell ref="AB22:AD22"/>
+    <mergeCell ref="L92:N92"/>
+    <mergeCell ref="T67:V68"/>
+    <mergeCell ref="I162:K162"/>
+    <mergeCell ref="T127:V127"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="AB118:AD119"/>
+    <mergeCell ref="Q32:S33"/>
+    <mergeCell ref="A67:C68"/>
+    <mergeCell ref="Y168:AD168"/>
+    <mergeCell ref="Q98:V98"/>
+    <mergeCell ref="I98:N98"/>
+    <mergeCell ref="Y27:AA27"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="A115:C115"/>
+    <mergeCell ref="L102:N103"/>
+    <mergeCell ref="I63:N63"/>
+    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A135:C136"/>
+    <mergeCell ref="Q50:S51"/>
+    <mergeCell ref="AB111:AD114"/>
+    <mergeCell ref="AB48:AD49"/>
+    <mergeCell ref="I116:N116"/>
+    <mergeCell ref="I123:N124"/>
+    <mergeCell ref="T41:V44"/>
+    <mergeCell ref="T153:V154"/>
+    <mergeCell ref="Y167:AA167"/>
+    <mergeCell ref="L23:N26"/>
+    <mergeCell ref="D83:F84"/>
+    <mergeCell ref="Q82:V82"/>
+    <mergeCell ref="T10:V10"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" fitToHeight="0" fitToWidth="1"/>
+  <rowBreaks count="4" manualBreakCount="4">
+    <brk id="34" min="0" max="16383" man="1"/>
+    <brk id="69" min="0" max="16383" man="1"/>
+    <brk id="104" min="0" max="16383" man="1"/>
+    <brk id="139" min="0" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
 
@@ -6134,10 +13986,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -6700,10 +14552,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7266,10 +15118,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7832,10 +15684,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8398,10 +16250,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -8964,10 +16816,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9530,10 +17382,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10096,10 +17948,10 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A16:G16"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
